--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAFBFBB-CDA1-44BF-9ED4-7E3995134E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028FA3A7-76DB-4B99-953D-D4DFB23D465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,11 @@
   </sheets>
   <definedNames>
     <definedName name="Cat">Dmart_Sales_Data[Category]</definedName>
+    <definedName name="CustomerT">Sheet1!$T$21</definedName>
     <definedName name="Discount">Dmart_Sales_Data[discount]</definedName>
+    <definedName name="Orders">Dmart_Sales_Data[[#Headers],[Column1]]</definedName>
+    <definedName name="Payment">Dmart_Sales_Data[[#Headers],[payment_mode]]</definedName>
+    <definedName name="RE">Dmart_Sales_Data[[#Headers],[Updated_Region]]</definedName>
     <definedName name="Regions">Dmart_Sales_Data[Region]</definedName>
     <definedName name="Saless">Dmart_Sales_Data[sales]</definedName>
   </definedNames>
@@ -66,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4673" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4683" uniqueCount="665">
   <si>
     <t>Column1</t>
   </si>
@@ -2031,6 +2035,36 @@
   </si>
   <si>
     <t>NO Category Sales</t>
+  </si>
+  <si>
+    <t>Total Orders</t>
+  </si>
+  <si>
+    <t>TRANSACTIONS DONE BY CARD</t>
+  </si>
+  <si>
+    <t>TRANSACTIONS DONE BY UPI</t>
+  </si>
+  <si>
+    <t>TRANSACTIONS DONE BY CASH</t>
+  </si>
+  <si>
+    <t>No.OF Transaction having Sales value&gt;4000</t>
+  </si>
+  <si>
+    <t>No.OF Transaction having Sales value&gt;4000 but region NORTH</t>
+  </si>
+  <si>
+    <t>No.OF Transaction having Sales value&gt;4000 but region EAST</t>
+  </si>
+  <si>
+    <t>No.OF Transaction having Sales value&gt;4000 but region WEST</t>
+  </si>
+  <si>
+    <t>No.OF Transaction having Sales value&gt;4000 but region SOUTH</t>
+  </si>
+  <si>
+    <t>Count of sales for custType Member and Payment UPI Or CARD</t>
   </si>
 </sst>
 </file>
@@ -2039,9 +2073,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2180,6 +2214,19 @@
       <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2336,7 +2383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2414,45 +2461,23 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="31">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF212529"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4F4F4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2520,6 +2545,31 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F4F4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
@@ -2546,7 +2596,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2554,56 +2604,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF212529"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4F4F4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12.3"/>
-        <color rgb="FF333333"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFD8D8D8"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2657,17 +2657,67 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="medium">
+          <color rgb="FFA4A4A4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF212529"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F4F4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FFA4A4A4"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FFA4A4A4"/>
-        </top>
-      </border>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12.3"/>
+        <color rgb="FF333333"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD8D8D8"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3077,16 +3127,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{97762E84-48E0-42EB-A297-65A392978E80}" name="Table3" displayName="Table3" ref="D2:H9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="10" headerRowBorderDxfId="12" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{97762E84-48E0-42EB-A297-65A392978E80}" name="Table3" displayName="Table3" ref="D2:H9" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
   <autoFilter ref="D2:H9" xr:uid="{97762E84-48E0-42EB-A297-65A392978E80}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{04D31066-1E3C-4184-8E77-38D4373C09E3}" name="Category" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{04D31066-1E3C-4184-8E77-38D4373C09E3}" name="Category" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{B4ED27EB-1280-4573-825E-1FAE5F5D223B}" name="Food" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{84AD34BF-6AB9-4F43-8B3A-631B286FA799}" name="Sales" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{B054319D-30B4-4366-9FD9-682FFDDFADA1}" name="FRUITSALES" dataDxfId="6">
       <calculatedColumnFormula>SUMIF(D3:D9,"=Fruits",F3:F9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE0E48A9-2D8C-40D1-8D6A-E2D571049241}" name="Column1" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{DE0E48A9-2D8C-40D1-8D6A-E2D571049241}" name="Column1" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3311,8 +3361,9 @@
     <col min="16" max="16" width="8.6640625" customWidth="1"/>
     <col min="17" max="17" width="12.88671875" customWidth="1"/>
     <col min="18" max="18" width="8.6640625" customWidth="1"/>
-    <col min="19" max="19" width="44.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="8.6640625" customWidth="1"/>
+    <col min="19" max="19" width="63.109375" customWidth="1"/>
+    <col min="20" max="20" width="19.44140625" customWidth="1"/>
+    <col min="21" max="23" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3502,7 +3553,7 @@
         <v>no</v>
       </c>
       <c r="R3" s="5"/>
-      <c r="S3" s="49">
+      <c r="S3" s="48">
         <f>SUMIF(M2:M500,"=UPI",E2:E500)</f>
         <v>386412.25</v>
       </c>
@@ -3639,7 +3690,7 @@
         <v>yes</v>
       </c>
       <c r="R5" s="5"/>
-      <c r="S5" s="49">
+      <c r="S5" s="48">
         <f>SUMIF(M2:M500,"=Cash",E2:E500)</f>
         <v>522964.3</v>
       </c>
@@ -3776,7 +3827,7 @@
         <v>yes</v>
       </c>
       <c r="R7" s="5"/>
-      <c r="S7" s="49">
+      <c r="S7" s="48">
         <f>SUMIF(M2:M500,"=Card",E2:E500)</f>
         <v>413292.63999999996</v>
       </c>
@@ -3977,7 +4028,7 @@
         <v>no</v>
       </c>
       <c r="R10" s="5"/>
-      <c r="S10" s="50" cm="1">
+      <c r="S10" s="49" cm="1">
         <f t="array" ref="S10">SUMIFS(Saless,Cat,"Electronics",Regions,"North",Discount,"&gt;0.40")</f>
         <v>36091.269999999997</v>
       </c>
@@ -4112,8 +4163,13 @@
         <v>no</v>
       </c>
       <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
+      <c r="S12" s="44" t="s">
+        <v>655</v>
+      </c>
+      <c r="T12" s="52">
+        <f>COUNT(Saless)</f>
+        <v>498</v>
+      </c>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
@@ -4178,8 +4234,13 @@
         <v>no</v>
       </c>
       <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
+      <c r="S13" s="44" t="s">
+        <v>657</v>
+      </c>
+      <c r="T13" s="52">
+        <f>COUNTIF(Dmart_Sales_Data[payment_mode],"=UPI")</f>
+        <v>149</v>
+      </c>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
@@ -4244,8 +4305,13 @@
         <v>no</v>
       </c>
       <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
+      <c r="S14" s="44" t="s">
+        <v>656</v>
+      </c>
+      <c r="T14" s="52">
+        <f>COUNTIF(Dmart_Sales_Data[payment_mode],"=CARD")</f>
+        <v>164</v>
+      </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
@@ -4310,8 +4376,13 @@
         <v>no</v>
       </c>
       <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="22"/>
+      <c r="S15" s="44" t="s">
+        <v>658</v>
+      </c>
+      <c r="T15" s="52">
+        <f>COUNTIF(Dmart_Sales_Data[payment_mode],"=Cash")</f>
+        <v>185</v>
+      </c>
       <c r="U15" s="22"/>
       <c r="V15" s="5"/>
       <c r="W15" s="5"/>
@@ -4376,8 +4447,13 @@
         <v>no</v>
       </c>
       <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="22"/>
+      <c r="S16" s="44" t="s">
+        <v>659</v>
+      </c>
+      <c r="T16" s="53" cm="1">
+        <f t="array" ref="T16">COUNTIF(Saless,"&gt;4000")</f>
+        <v>115</v>
+      </c>
       <c r="U16" s="22"/>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
@@ -4442,8 +4518,13 @@
         <v>yes</v>
       </c>
       <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="22"/>
+      <c r="S17" s="44" t="s">
+        <v>660</v>
+      </c>
+      <c r="T17" s="53" cm="1">
+        <f t="array" ref="T17">COUNTIFS(Saless,"&gt;4000",Regions,"=North")</f>
+        <v>32</v>
+      </c>
       <c r="U17" s="22"/>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
@@ -4508,8 +4589,13 @@
         <v>yes</v>
       </c>
       <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="22"/>
+      <c r="S18" s="44" t="s">
+        <v>661</v>
+      </c>
+      <c r="T18" s="53" cm="1">
+        <f t="array" ref="T18">COUNTIFS(Saless,"&gt;4000",Regions,"=East")</f>
+        <v>29</v>
+      </c>
       <c r="U18" s="22"/>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
@@ -4574,8 +4660,13 @@
         <v>no</v>
       </c>
       <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
+      <c r="S19" s="44" t="s">
+        <v>662</v>
+      </c>
+      <c r="T19" s="53" cm="1">
+        <f t="array" ref="T19">COUNTIFS(Saless,"&gt;4000",Regions,"=West")</f>
+        <v>27</v>
+      </c>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
@@ -4640,8 +4731,13 @@
         <v>yes</v>
       </c>
       <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
+      <c r="S20" s="44" t="s">
+        <v>663</v>
+      </c>
+      <c r="T20" s="53" cm="1">
+        <f t="array" ref="T20">COUNTIFS(Saless,"&gt;4000",Regions,"=South")</f>
+        <v>27</v>
+      </c>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
       <c r="W20" s="5"/>
@@ -4706,7 +4802,7 @@
         <v>no</v>
       </c>
       <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
+      <c r="S21" s="50"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
@@ -4772,8 +4868,13 @@
         <v>no</v>
       </c>
       <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
+      <c r="S22" s="44" t="s">
+        <v>664</v>
+      </c>
+      <c r="T22" s="51">
+        <f>COUNTIFS(Dmart_Sales_Data[customer_type],"Member",Dmart_Sales_Data[payment_mode],"UPI")+COUNTIFS(Dmart_Sales_Data[customer_type],"Member",Dmart_Sales_Data[payment_mode],"Card")</f>
+        <v>97</v>
+      </c>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
@@ -48793,8 +48894,8 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="E1:E1048576 F1:F499">
-    <cfRule type="top10" dxfId="5" priority="2" bottom="1" rank="10"/>
-    <cfRule type="top10" dxfId="4" priority="3" rank="10"/>
+    <cfRule type="top10" dxfId="4" priority="2" bottom="1" rank="10"/>
+    <cfRule type="top10" dxfId="3" priority="3" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F500:F1048576 G1:G499">
     <cfRule type="colorScale" priority="4">
@@ -48809,7 +48910,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H499 G500:G1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49251,7 +49352,7 @@
       <c r="F4" s="47">
         <v>30</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="45">
         <f>SUMIF(D3:D9,"",F3:F9)</f>
         <v>430</v>
       </c>
@@ -49972,10 +50073,10 @@
   </sortState>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="E2:E9">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>50000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>50000</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028FA3A7-76DB-4B99-953D-D4DFB23D465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1372F2B4-96DF-41FA-AEF6-F80B7D46F7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,13 @@
     <sheet name="Sheet7" sheetId="8" r:id="rId6"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId7"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet7!$B$2:$B$8</definedName>
     <definedName name="Cat">Dmart_Sales_Data[Category]</definedName>
     <definedName name="CustomerT">Sheet1!$T$21</definedName>
+    <definedName name="Dateo">Dmart_Sales_Data[[#Headers],[order_date]]</definedName>
     <definedName name="Discount">Dmart_Sales_Data[discount]</definedName>
     <definedName name="Orders">Dmart_Sales_Data[[#Headers],[Column1]]</definedName>
     <definedName name="Payment">Dmart_Sales_Data[[#Headers],[payment_mode]]</definedName>
@@ -70,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4683" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4732" uniqueCount="685">
   <si>
     <t>Column1</t>
   </si>
@@ -2065,6 +2068,66 @@
   </si>
   <si>
     <t>Count of sales for custType Member and Payment UPI Or CARD</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Total Sales For North</t>
+  </si>
+  <si>
+    <t>Total Sales For East</t>
+  </si>
+  <si>
+    <t>Total Sales For West</t>
+  </si>
+  <si>
+    <t>Total Sales For South</t>
+  </si>
+  <si>
+    <t>No.of Orders North</t>
+  </si>
+  <si>
+    <t>No.of Orders South</t>
+  </si>
+  <si>
+    <t>No.of Orders East</t>
+  </si>
+  <si>
+    <t>No.of Orders West</t>
+  </si>
+  <si>
+    <t>Total Sales for 2023</t>
+  </si>
+  <si>
+    <t>Last Six months Sales</t>
+  </si>
+  <si>
+    <t>Max date</t>
+  </si>
+  <si>
+    <t>EmpID</t>
+  </si>
+  <si>
+    <t>Find Duplicates in Employee ID</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Total Sales Using Sub Total</t>
+  </si>
+  <si>
+    <t>EmployeeID</t>
+  </si>
+  <si>
+    <t>Using Index Match</t>
+  </si>
+  <si>
+    <t>Using Match</t>
   </si>
 </sst>
 </file>
@@ -2075,12 +2138,19 @@
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2229,8 +2299,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2261,8 +2338,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2376,60 +2471,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2438,46 +2546,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="32">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2718,6 +2845,27 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3097,30 +3245,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Dmart_Sales_Data" displayName="Dmart_Sales_Data" ref="A1:Q499" totalsRowShown="0">
-  <autoFilter ref="A1:Q499" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Region" dataDxfId="29"/>
-    <tableColumn id="14" xr3:uid="{477EC3EE-5C02-49E7-BF3C-70769E0D14F5}" name="Updated_Region" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Category" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="sales" dataDxfId="26"/>
-    <tableColumn id="16" xr3:uid="{DD01BA02-433B-442A-BA17-28274E40D36E}" name="Sales_Range" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Dmart_Sales_Data" displayName="Dmart_Sales_Data" ref="A1:R499" totalsRowShown="0">
+  <autoFilter ref="A1:R499" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Region" dataDxfId="30"/>
+    <tableColumn id="14" xr3:uid="{477EC3EE-5C02-49E7-BF3C-70769E0D14F5}" name="Updated_Region" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Category" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="sales" dataDxfId="27"/>
+    <tableColumn id="16" xr3:uid="{DD01BA02-433B-442A-BA17-28274E40D36E}" name="Sales_Range" dataDxfId="26">
       <calculatedColumnFormula>IF(Dmart_Sales_Data[[#This Row],[sales]]&lt;1000,"LowSales",IF(Dmart_Sales_Data[[#This Row],[sales]]&lt;2000,"MediumSales",IF(Dmart_Sales_Data[[#This Row],[sales]]&gt;3000,"HighSales")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="discount" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="quantity" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="order_date" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="delivery_date" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="customer_type" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="customer_type2" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="payment_mode" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="profit" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Updated_City" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="city" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{7963F693-B339-40DA-A36A-56075F49611F}" name="discount_given" dataDxfId="14">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="discount" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="quantity" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="order_date" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="delivery_date" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="customer_type" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="customer_type2" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="payment_mode" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="profit" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Updated_City" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="city" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{7963F693-B339-40DA-A36A-56075F49611F}" name="discount_given" dataDxfId="15">
       <calculatedColumnFormula>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="18" xr3:uid="{604EF363-6AE2-4859-8F1F-1086D7E04A1E}" name="Column2" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3360,9 +3509,9 @@
     <col min="15" max="15" width="12.6640625" customWidth="1"/>
     <col min="16" max="16" width="8.6640625" customWidth="1"/>
     <col min="17" max="17" width="12.88671875" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="19.77734375" customWidth="1"/>
     <col min="19" max="19" width="63.109375" customWidth="1"/>
-    <col min="20" max="20" width="19.44140625" customWidth="1"/>
+    <col min="20" max="20" width="22.88671875" customWidth="1"/>
     <col min="21" max="23" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3418,7 +3567,9 @@
       <c r="Q1" s="42" t="s">
         <v>638</v>
       </c>
-      <c r="R1" s="5"/>
+      <c r="R1" s="42" t="s">
+        <v>665</v>
+      </c>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
@@ -3484,7 +3635,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R2" s="5"/>
+      <c r="R2" s="43"/>
       <c r="S2" s="44" t="s">
         <v>640</v>
       </c>
@@ -3552,7 +3703,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R3" s="5"/>
+      <c r="R3" s="43"/>
       <c r="S3" s="48">
         <f>SUMIF(M2:M500,"=UPI",E2:E500)</f>
         <v>386412.25</v>
@@ -3621,7 +3772,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R4" s="5"/>
+      <c r="R4" s="43"/>
       <c r="S4" s="44" t="s">
         <v>641</v>
       </c>
@@ -3689,7 +3840,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R5" s="5"/>
+      <c r="R5" s="43"/>
       <c r="S5" s="48">
         <f>SUMIF(M2:M500,"=Cash",E2:E500)</f>
         <v>522964.3</v>
@@ -3758,7 +3909,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R6" s="5"/>
+      <c r="R6" s="43"/>
       <c r="S6" s="44" t="s">
         <v>642</v>
       </c>
@@ -3826,7 +3977,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R7" s="5"/>
+      <c r="R7" s="43"/>
       <c r="S7" s="48">
         <f>SUMIF(M2:M500,"=Card",E2:E500)</f>
         <v>413292.63999999996</v>
@@ -3895,7 +4046,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R8" s="5"/>
+      <c r="R8" s="43"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
@@ -3961,7 +4112,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R9" s="5"/>
+      <c r="R9" s="43"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
@@ -4027,7 +4178,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R10" s="5"/>
+      <c r="R10" s="43"/>
       <c r="S10" s="49" cm="1">
         <f t="array" ref="S10">SUMIFS(Saless,Cat,"Electronics",Regions,"North",Discount,"&gt;0.40")</f>
         <v>36091.269999999997</v>
@@ -4096,7 +4247,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R11" s="5"/>
+      <c r="R11" s="43"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
@@ -4162,7 +4313,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R12" s="5"/>
+      <c r="R12" s="43"/>
       <c r="S12" s="44" t="s">
         <v>655</v>
       </c>
@@ -4233,7 +4384,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R13" s="5"/>
+      <c r="R13" s="43"/>
       <c r="S13" s="44" t="s">
         <v>657</v>
       </c>
@@ -4304,7 +4455,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R14" s="5"/>
+      <c r="R14" s="43"/>
       <c r="S14" s="44" t="s">
         <v>656</v>
       </c>
@@ -4375,7 +4526,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R15" s="5"/>
+      <c r="R15" s="43"/>
       <c r="S15" s="44" t="s">
         <v>658</v>
       </c>
@@ -4446,7 +4597,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R16" s="5"/>
+      <c r="R16" s="43"/>
       <c r="S16" s="44" t="s">
         <v>659</v>
       </c>
@@ -4517,7 +4668,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R17" s="5"/>
+      <c r="R17" s="43"/>
       <c r="S17" s="44" t="s">
         <v>660</v>
       </c>
@@ -4588,7 +4739,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R18" s="5"/>
+      <c r="R18" s="43"/>
       <c r="S18" s="44" t="s">
         <v>661</v>
       </c>
@@ -4659,7 +4810,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R19" s="5"/>
+      <c r="R19" s="43"/>
       <c r="S19" s="44" t="s">
         <v>662</v>
       </c>
@@ -4730,7 +4881,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R20" s="5"/>
+      <c r="R20" s="43"/>
       <c r="S20" s="44" t="s">
         <v>663</v>
       </c>
@@ -4801,7 +4952,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R21" s="5"/>
+      <c r="R21" s="43"/>
       <c r="S21" s="50"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
@@ -4867,11 +5018,11 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R22" s="5"/>
+      <c r="R22" s="43"/>
       <c r="S22" s="44" t="s">
         <v>664</v>
       </c>
-      <c r="T22" s="51">
+      <c r="T22" s="52">
         <f>COUNTIFS(Dmart_Sales_Data[customer_type],"Member",Dmart_Sales_Data[payment_mode],"UPI")+COUNTIFS(Dmart_Sales_Data[customer_type],"Member",Dmart_Sales_Data[payment_mode],"Card")</f>
         <v>97</v>
       </c>
@@ -4938,7 +5089,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R23" s="5"/>
+      <c r="R23" s="43"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5"/>
       <c r="U23" s="5"/>
@@ -5004,9 +5155,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="44" t="s">
+        <v>666</v>
+      </c>
+      <c r="T24" s="52" cm="1">
+        <f t="array" ref="T24">SUMIF(Regions,"=North",Saless)</f>
+        <v>334964.16000000003</v>
+      </c>
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
@@ -5070,9 +5226,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="44" t="s">
+        <v>667</v>
+      </c>
+      <c r="T25" s="52" cm="1">
+        <f t="array" ref="T25">SUMIF(Regions,"=East",Saless)</f>
+        <v>337881.26999999996</v>
+      </c>
       <c r="U25" s="5"/>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
@@ -5136,9 +5297,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="44" t="s">
+        <v>668</v>
+      </c>
+      <c r="T26" s="52" cm="1">
+        <f t="array" ref="T26">SUMIF(Regions,"=West",Saless)</f>
+        <v>346200.06999999983</v>
+      </c>
       <c r="U26" s="5"/>
       <c r="V26" s="5"/>
       <c r="W26" s="5"/>
@@ -5202,9 +5368,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="44" t="s">
+        <v>669</v>
+      </c>
+      <c r="T27" s="52" cm="1">
+        <f t="array" ref="T27">SUMIF(Regions,"=South",Saless)</f>
+        <v>303623.68999999994</v>
+      </c>
       <c r="U27" s="5"/>
       <c r="V27" s="5"/>
       <c r="W27" s="5"/>
@@ -5268,7 +5439,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R28" s="5"/>
+      <c r="R28" s="43"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -5334,9 +5505,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="44" t="s">
+        <v>670</v>
+      </c>
+      <c r="T29" s="52" cm="1">
+        <f t="array" ref="T29">COUNTIF(Regions,"North")</f>
+        <v>124</v>
+      </c>
       <c r="U29" s="5"/>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
@@ -5400,9 +5576,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="44" t="s">
+        <v>671</v>
+      </c>
+      <c r="T30" s="52" cm="1">
+        <f t="array" ref="T30">COUNTIF(Regions,"South")</f>
+        <v>124</v>
+      </c>
       <c r="U30" s="5"/>
       <c r="V30" s="5"/>
       <c r="W30" s="5"/>
@@ -5466,9 +5647,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="44" t="s">
+        <v>672</v>
+      </c>
+      <c r="T31" s="52" cm="1">
+        <f t="array" ref="T31">COUNTIF(Regions,"East")</f>
+        <v>125</v>
+      </c>
       <c r="U31" s="5"/>
       <c r="V31" s="5"/>
       <c r="W31" s="5"/>
@@ -5532,9 +5718,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="44" t="s">
+        <v>673</v>
+      </c>
+      <c r="T32" s="52" cm="1">
+        <f t="array" ref="T32">COUNTIF(Regions,"West")</f>
+        <v>125</v>
+      </c>
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
       <c r="W32" s="5"/>
@@ -5598,7 +5789,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R33" s="5"/>
+      <c r="R33" s="43"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
@@ -5664,10 +5855,15 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="U34" s="5"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="44" t="s">
+        <v>674</v>
+      </c>
+      <c r="T34" s="52" cm="1">
+        <f t="array" ref="T34">SUMIF(Dmart_Sales_Data[order_date],"&lt;2024-01-01",Saless)</f>
+        <v>654586.69000000018</v>
+      </c>
+      <c r="U34" s="51"/>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
@@ -5730,10 +5926,18 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="5"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="44" t="s">
+        <v>675</v>
+      </c>
+      <c r="T35" s="52" cm="1">
+        <f t="array" ref="T35">SUMIF(Dmart_Sales_Data[order_date],"&gt;=2024-07-01",Saless)</f>
+        <v>368049.34999999992</v>
+      </c>
+      <c r="U35" s="52" cm="1">
+        <f t="array" ref="U35">SUMIFS(Saless,Dmart_Sales_Data[order_date],"&gt;=2024-07-01",Dmart_Sales_Data[order_date],"&lt;=2024-12-31")</f>
+        <v>368049.34999999992</v>
+      </c>
       <c r="V35" s="5"/>
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
@@ -5796,10 +6000,15 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-      <c r="U36" s="5"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="44" t="s">
+        <v>676</v>
+      </c>
+      <c r="T36" s="55">
+        <f>MAX(Dateo,Saless)</f>
+        <v>4997.47</v>
+      </c>
+      <c r="U36" s="52"/>
       <c r="V36" s="5"/>
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
@@ -5862,7 +6071,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R37" s="5"/>
+      <c r="R37" s="43"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
@@ -5928,9 +6137,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="50" t="s">
+        <v>680</v>
+      </c>
+      <c r="T38" s="54">
+        <f>SUM(Saless)</f>
+        <v>1322669.1900000023</v>
+      </c>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
@@ -5994,9 +6208,14 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="50" t="s">
+        <v>681</v>
+      </c>
+      <c r="T39" s="54" cm="1">
+        <f t="array" ref="T39">SUBTOTAL(9,Saless)</f>
+        <v>1322669.1900000023</v>
+      </c>
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
@@ -6060,7 +6279,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R40" s="5"/>
+      <c r="R40" s="43"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
@@ -6126,7 +6345,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R41" s="5"/>
+      <c r="R41" s="43"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
@@ -6192,7 +6411,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R42" s="5"/>
+      <c r="R42" s="43"/>
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
@@ -6258,7 +6477,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R43" s="5"/>
+      <c r="R43" s="43"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
@@ -6324,7 +6543,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R44" s="5"/>
+      <c r="R44" s="43"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
@@ -6390,7 +6609,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R45" s="5"/>
+      <c r="R45" s="43"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -6456,7 +6675,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R46" s="5"/>
+      <c r="R46" s="43"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
@@ -6522,7 +6741,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R47" s="5"/>
+      <c r="R47" s="43"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -6588,7 +6807,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R48" s="5"/>
+      <c r="R48" s="43"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -6654,7 +6873,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R49" s="5"/>
+      <c r="R49" s="43"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
@@ -6720,7 +6939,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R50" s="5"/>
+      <c r="R50" s="43"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
@@ -6786,7 +7005,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R51" s="5"/>
+      <c r="R51" s="43"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5"/>
       <c r="U51" s="5"/>
@@ -6852,7 +7071,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R52" s="5"/>
+      <c r="R52" s="43"/>
       <c r="S52" s="5"/>
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
@@ -6918,7 +7137,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R53" s="5"/>
+      <c r="R53" s="43"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5"/>
       <c r="U53" s="5"/>
@@ -6984,7 +7203,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R54" s="5"/>
+      <c r="R54" s="43"/>
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
       <c r="U54" s="5"/>
@@ -7050,7 +7269,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R55" s="5"/>
+      <c r="R55" s="43"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5"/>
       <c r="U55" s="5"/>
@@ -7116,7 +7335,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R56" s="5"/>
+      <c r="R56" s="43"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
       <c r="U56" s="5"/>
@@ -7182,7 +7401,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R57" s="5"/>
+      <c r="R57" s="43"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
@@ -7248,7 +7467,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R58" s="5"/>
+      <c r="R58" s="43"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
@@ -7314,7 +7533,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R59" s="5"/>
+      <c r="R59" s="43"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
@@ -7380,7 +7599,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R60" s="5"/>
+      <c r="R60" s="43"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5"/>
       <c r="U60" s="5"/>
@@ -7446,7 +7665,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R61" s="5"/>
+      <c r="R61" s="43"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
       <c r="U61" s="5"/>
@@ -7512,7 +7731,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R62" s="5"/>
+      <c r="R62" s="43"/>
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
       <c r="U62" s="5"/>
@@ -7578,7 +7797,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R63" s="5"/>
+      <c r="R63" s="43"/>
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
       <c r="U63" s="5"/>
@@ -7644,7 +7863,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R64" s="5"/>
+      <c r="R64" s="43"/>
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
       <c r="U64" s="5"/>
@@ -7710,7 +7929,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R65" s="5"/>
+      <c r="R65" s="43"/>
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
       <c r="U65" s="5"/>
@@ -7776,7 +7995,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R66" s="5"/>
+      <c r="R66" s="43"/>
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
       <c r="U66" s="5"/>
@@ -7842,7 +8061,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R67" s="5"/>
+      <c r="R67" s="43"/>
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
       <c r="U67" s="5"/>
@@ -7908,7 +8127,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R68" s="5"/>
+      <c r="R68" s="43"/>
       <c r="S68" s="5"/>
       <c r="T68" s="5"/>
       <c r="U68" s="5"/>
@@ -7974,7 +8193,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R69" s="5"/>
+      <c r="R69" s="43"/>
       <c r="S69" s="5"/>
       <c r="T69" s="5"/>
       <c r="U69" s="5"/>
@@ -8040,7 +8259,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R70" s="5"/>
+      <c r="R70" s="43"/>
       <c r="S70" s="5"/>
       <c r="T70" s="5"/>
       <c r="U70" s="5"/>
@@ -8106,7 +8325,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R71" s="5"/>
+      <c r="R71" s="43"/>
       <c r="S71" s="5"/>
       <c r="T71" s="5"/>
       <c r="U71" s="5"/>
@@ -8172,7 +8391,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R72" s="5"/>
+      <c r="R72" s="43"/>
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
       <c r="U72" s="5"/>
@@ -8238,7 +8457,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R73" s="5"/>
+      <c r="R73" s="43"/>
       <c r="S73" s="5"/>
       <c r="T73" s="5"/>
       <c r="U73" s="5"/>
@@ -8304,7 +8523,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R74" s="5"/>
+      <c r="R74" s="43"/>
       <c r="S74" s="5"/>
       <c r="T74" s="5"/>
       <c r="U74" s="5"/>
@@ -8370,7 +8589,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R75" s="5"/>
+      <c r="R75" s="43"/>
       <c r="S75" s="5"/>
       <c r="T75" s="5"/>
       <c r="U75" s="5"/>
@@ -8436,7 +8655,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R76" s="5"/>
+      <c r="R76" s="43"/>
       <c r="S76" s="5"/>
       <c r="T76" s="5"/>
       <c r="U76" s="5"/>
@@ -8502,7 +8721,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R77" s="5"/>
+      <c r="R77" s="43"/>
       <c r="S77" s="5"/>
       <c r="T77" s="5"/>
       <c r="U77" s="5"/>
@@ -8568,7 +8787,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R78" s="5"/>
+      <c r="R78" s="43"/>
       <c r="S78" s="5"/>
       <c r="T78" s="5"/>
       <c r="U78" s="5"/>
@@ -8634,7 +8853,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R79" s="5"/>
+      <c r="R79" s="43"/>
       <c r="S79" s="5"/>
       <c r="T79" s="5"/>
       <c r="U79" s="5"/>
@@ -8700,7 +8919,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R80" s="5"/>
+      <c r="R80" s="43"/>
       <c r="S80" s="5"/>
       <c r="T80" s="5"/>
       <c r="U80" s="5"/>
@@ -8766,7 +8985,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R81" s="5"/>
+      <c r="R81" s="43"/>
       <c r="S81" s="5"/>
       <c r="T81" s="5"/>
       <c r="U81" s="5"/>
@@ -8832,7 +9051,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R82" s="5"/>
+      <c r="R82" s="43"/>
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
       <c r="U82" s="5"/>
@@ -8898,7 +9117,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R83" s="5"/>
+      <c r="R83" s="43"/>
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
       <c r="U83" s="5"/>
@@ -8964,7 +9183,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R84" s="5"/>
+      <c r="R84" s="43"/>
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
       <c r="U84" s="5"/>
@@ -9030,7 +9249,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R85" s="5"/>
+      <c r="R85" s="43"/>
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
       <c r="U85" s="5"/>
@@ -9096,7 +9315,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R86" s="5"/>
+      <c r="R86" s="43"/>
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
       <c r="U86" s="5"/>
@@ -9162,7 +9381,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R87" s="5"/>
+      <c r="R87" s="43"/>
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
       <c r="U87" s="5"/>
@@ -9228,7 +9447,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R88" s="5"/>
+      <c r="R88" s="43"/>
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
       <c r="U88" s="5"/>
@@ -9294,7 +9513,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R89" s="5"/>
+      <c r="R89" s="43"/>
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
       <c r="U89" s="5"/>
@@ -9360,7 +9579,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R90" s="5"/>
+      <c r="R90" s="43"/>
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
       <c r="U90" s="5"/>
@@ -9426,7 +9645,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R91" s="5"/>
+      <c r="R91" s="43"/>
       <c r="S91" s="5"/>
       <c r="T91" s="5"/>
       <c r="U91" s="5"/>
@@ -9492,7 +9711,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R92" s="5"/>
+      <c r="R92" s="43"/>
       <c r="S92" s="5"/>
       <c r="T92" s="5"/>
       <c r="U92" s="5"/>
@@ -9558,7 +9777,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R93" s="5"/>
+      <c r="R93" s="43"/>
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
       <c r="U93" s="5"/>
@@ -9624,7 +9843,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R94" s="5"/>
+      <c r="R94" s="43"/>
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
       <c r="U94" s="5"/>
@@ -9690,7 +9909,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R95" s="5"/>
+      <c r="R95" s="43"/>
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
       <c r="U95" s="5"/>
@@ -9756,7 +9975,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R96" s="5"/>
+      <c r="R96" s="43"/>
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
       <c r="U96" s="5"/>
@@ -9822,7 +10041,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R97" s="5"/>
+      <c r="R97" s="43"/>
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
       <c r="U97" s="5"/>
@@ -9888,7 +10107,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R98" s="5"/>
+      <c r="R98" s="43"/>
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
       <c r="U98" s="5"/>
@@ -9954,7 +10173,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R99" s="5"/>
+      <c r="R99" s="43"/>
       <c r="S99" s="5"/>
       <c r="T99" s="5"/>
       <c r="U99" s="5"/>
@@ -10020,7 +10239,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R100" s="5"/>
+      <c r="R100" s="43"/>
       <c r="S100" s="5"/>
       <c r="T100" s="5"/>
       <c r="U100" s="5"/>
@@ -10086,7 +10305,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R101" s="5"/>
+      <c r="R101" s="43"/>
       <c r="S101" s="5"/>
       <c r="T101" s="5"/>
       <c r="U101" s="5"/>
@@ -10152,7 +10371,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R102" s="5"/>
+      <c r="R102" s="43"/>
       <c r="S102" s="5"/>
       <c r="T102" s="5"/>
       <c r="U102" s="5"/>
@@ -10218,7 +10437,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R103" s="5"/>
+      <c r="R103" s="43"/>
       <c r="S103" s="5"/>
       <c r="T103" s="5"/>
       <c r="U103" s="5"/>
@@ -10284,7 +10503,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R104" s="5"/>
+      <c r="R104" s="43"/>
       <c r="S104" s="5"/>
       <c r="T104" s="5"/>
       <c r="U104" s="5"/>
@@ -10350,7 +10569,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R105" s="5"/>
+      <c r="R105" s="43"/>
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
       <c r="U105" s="5"/>
@@ -10416,7 +10635,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R106" s="5"/>
+      <c r="R106" s="43"/>
       <c r="S106" s="5"/>
       <c r="T106" s="5"/>
       <c r="U106" s="5"/>
@@ -10482,7 +10701,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R107" s="5"/>
+      <c r="R107" s="43"/>
       <c r="S107" s="5"/>
       <c r="T107" s="5"/>
       <c r="U107" s="5"/>
@@ -10548,7 +10767,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R108" s="5"/>
+      <c r="R108" s="43"/>
       <c r="S108" s="5"/>
       <c r="T108" s="5"/>
       <c r="U108" s="5"/>
@@ -10614,7 +10833,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R109" s="5"/>
+      <c r="R109" s="43"/>
       <c r="S109" s="5"/>
       <c r="T109" s="5"/>
       <c r="U109" s="5"/>
@@ -10680,7 +10899,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R110" s="5"/>
+      <c r="R110" s="43"/>
       <c r="S110" s="5"/>
       <c r="T110" s="5"/>
       <c r="U110" s="5"/>
@@ -10746,7 +10965,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R111" s="5"/>
+      <c r="R111" s="43"/>
       <c r="S111" s="5"/>
       <c r="T111" s="5"/>
       <c r="U111" s="5"/>
@@ -10812,7 +11031,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R112" s="5"/>
+      <c r="R112" s="43"/>
       <c r="S112" s="5"/>
       <c r="T112" s="5"/>
       <c r="U112" s="5"/>
@@ -10878,7 +11097,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R113" s="5"/>
+      <c r="R113" s="43"/>
       <c r="S113" s="5"/>
       <c r="T113" s="5"/>
       <c r="U113" s="5"/>
@@ -10944,7 +11163,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R114" s="5"/>
+      <c r="R114" s="43"/>
       <c r="S114" s="5"/>
       <c r="T114" s="5"/>
       <c r="U114" s="5"/>
@@ -11010,7 +11229,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R115" s="5"/>
+      <c r="R115" s="43"/>
       <c r="S115" s="5"/>
       <c r="T115" s="5"/>
       <c r="U115" s="5"/>
@@ -11076,7 +11295,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R116" s="5"/>
+      <c r="R116" s="43"/>
       <c r="S116" s="5"/>
       <c r="T116" s="5"/>
       <c r="U116" s="5"/>
@@ -11142,7 +11361,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R117" s="5"/>
+      <c r="R117" s="43"/>
       <c r="S117" s="5"/>
       <c r="T117" s="5"/>
       <c r="U117" s="5"/>
@@ -11208,7 +11427,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R118" s="5"/>
+      <c r="R118" s="43"/>
       <c r="S118" s="5"/>
       <c r="T118" s="5"/>
       <c r="U118" s="5"/>
@@ -11274,7 +11493,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R119" s="5"/>
+      <c r="R119" s="43"/>
       <c r="S119" s="5"/>
       <c r="T119" s="5"/>
       <c r="U119" s="5"/>
@@ -11340,7 +11559,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R120" s="5"/>
+      <c r="R120" s="43"/>
       <c r="S120" s="5"/>
       <c r="T120" s="5"/>
       <c r="U120" s="5"/>
@@ -11406,7 +11625,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R121" s="5"/>
+      <c r="R121" s="43"/>
       <c r="S121" s="5"/>
       <c r="T121" s="5"/>
       <c r="U121" s="5"/>
@@ -11472,7 +11691,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R122" s="5"/>
+      <c r="R122" s="43"/>
       <c r="S122" s="5"/>
       <c r="T122" s="5"/>
       <c r="U122" s="5"/>
@@ -11538,7 +11757,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R123" s="5"/>
+      <c r="R123" s="43"/>
       <c r="S123" s="5"/>
       <c r="T123" s="5"/>
       <c r="U123" s="5"/>
@@ -11604,7 +11823,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R124" s="5"/>
+      <c r="R124" s="43"/>
       <c r="S124" s="5"/>
       <c r="T124" s="5"/>
       <c r="U124" s="5"/>
@@ -11670,7 +11889,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R125" s="5"/>
+      <c r="R125" s="43"/>
       <c r="S125" s="5"/>
       <c r="T125" s="5"/>
       <c r="U125" s="5"/>
@@ -11736,7 +11955,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R126" s="5"/>
+      <c r="R126" s="43"/>
       <c r="S126" s="5"/>
       <c r="T126" s="5"/>
       <c r="U126" s="5"/>
@@ -11802,7 +12021,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R127" s="5"/>
+      <c r="R127" s="43"/>
       <c r="S127" s="5"/>
       <c r="T127" s="5"/>
       <c r="U127" s="5"/>
@@ -11868,7 +12087,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R128" s="5"/>
+      <c r="R128" s="43"/>
       <c r="S128" s="5"/>
       <c r="T128" s="5"/>
       <c r="U128" s="5"/>
@@ -11934,7 +12153,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R129" s="5"/>
+      <c r="R129" s="43"/>
       <c r="S129" s="5"/>
       <c r="T129" s="5"/>
       <c r="U129" s="5"/>
@@ -12000,7 +12219,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R130" s="5"/>
+      <c r="R130" s="43"/>
       <c r="S130" s="5"/>
       <c r="T130" s="5"/>
       <c r="U130" s="5"/>
@@ -12066,7 +12285,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R131" s="5"/>
+      <c r="R131" s="43"/>
       <c r="S131" s="5"/>
       <c r="T131" s="5"/>
       <c r="U131" s="5"/>
@@ -12132,7 +12351,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R132" s="5"/>
+      <c r="R132" s="43"/>
       <c r="S132" s="5"/>
       <c r="T132" s="5"/>
       <c r="U132" s="5"/>
@@ -12198,7 +12417,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R133" s="5"/>
+      <c r="R133" s="43"/>
       <c r="S133" s="5"/>
       <c r="T133" s="5"/>
       <c r="U133" s="5"/>
@@ -12264,7 +12483,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R134" s="5"/>
+      <c r="R134" s="43"/>
       <c r="S134" s="5"/>
       <c r="T134" s="5"/>
       <c r="U134" s="5"/>
@@ -12330,7 +12549,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R135" s="5"/>
+      <c r="R135" s="43"/>
       <c r="S135" s="5"/>
       <c r="T135" s="5"/>
       <c r="U135" s="5"/>
@@ -12396,7 +12615,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R136" s="5"/>
+      <c r="R136" s="43"/>
       <c r="S136" s="5"/>
       <c r="T136" s="5"/>
       <c r="U136" s="5"/>
@@ -12462,7 +12681,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R137" s="5"/>
+      <c r="R137" s="43"/>
       <c r="S137" s="5"/>
       <c r="T137" s="5"/>
       <c r="U137" s="5"/>
@@ -12528,7 +12747,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R138" s="5"/>
+      <c r="R138" s="43"/>
       <c r="S138" s="5"/>
       <c r="T138" s="5"/>
       <c r="U138" s="5"/>
@@ -12594,7 +12813,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R139" s="5"/>
+      <c r="R139" s="43"/>
       <c r="S139" s="5"/>
       <c r="T139" s="5"/>
       <c r="U139" s="5"/>
@@ -12660,7 +12879,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R140" s="5"/>
+      <c r="R140" s="43"/>
       <c r="S140" s="5"/>
       <c r="T140" s="5"/>
       <c r="U140" s="5"/>
@@ -12726,7 +12945,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R141" s="5"/>
+      <c r="R141" s="43"/>
       <c r="S141" s="5"/>
       <c r="T141" s="5"/>
       <c r="U141" s="5"/>
@@ -12792,7 +13011,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R142" s="5"/>
+      <c r="R142" s="43"/>
       <c r="S142" s="5"/>
       <c r="T142" s="5"/>
       <c r="U142" s="5"/>
@@ -12858,7 +13077,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R143" s="5"/>
+      <c r="R143" s="43"/>
       <c r="S143" s="5"/>
       <c r="T143" s="5"/>
       <c r="U143" s="5"/>
@@ -12924,7 +13143,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R144" s="5"/>
+      <c r="R144" s="43"/>
       <c r="S144" s="5"/>
       <c r="T144" s="5"/>
       <c r="U144" s="5"/>
@@ -12990,7 +13209,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R145" s="5"/>
+      <c r="R145" s="43"/>
       <c r="S145" s="5"/>
       <c r="T145" s="5"/>
       <c r="U145" s="5"/>
@@ -13056,7 +13275,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R146" s="5"/>
+      <c r="R146" s="43"/>
       <c r="S146" s="5"/>
       <c r="T146" s="5"/>
       <c r="U146" s="5"/>
@@ -13122,7 +13341,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R147" s="5"/>
+      <c r="R147" s="43"/>
       <c r="S147" s="5"/>
       <c r="T147" s="5"/>
       <c r="U147" s="5"/>
@@ -13188,7 +13407,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R148" s="5"/>
+      <c r="R148" s="43"/>
       <c r="S148" s="5"/>
       <c r="T148" s="5"/>
       <c r="U148" s="5"/>
@@ -13254,7 +13473,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R149" s="5"/>
+      <c r="R149" s="43"/>
       <c r="S149" s="5"/>
       <c r="T149" s="5"/>
       <c r="U149" s="5"/>
@@ -13320,7 +13539,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R150" s="5"/>
+      <c r="R150" s="43"/>
       <c r="S150" s="5"/>
       <c r="T150" s="5"/>
       <c r="U150" s="5"/>
@@ -13386,7 +13605,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R151" s="5"/>
+      <c r="R151" s="43"/>
       <c r="S151" s="5"/>
       <c r="T151" s="5"/>
       <c r="U151" s="5"/>
@@ -13452,7 +13671,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R152" s="5"/>
+      <c r="R152" s="43"/>
       <c r="S152" s="5"/>
       <c r="T152" s="5"/>
       <c r="U152" s="5"/>
@@ -13518,7 +13737,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R153" s="5"/>
+      <c r="R153" s="43"/>
       <c r="S153" s="5"/>
       <c r="T153" s="5"/>
       <c r="U153" s="5"/>
@@ -13584,7 +13803,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R154" s="5"/>
+      <c r="R154" s="43"/>
       <c r="S154" s="5"/>
       <c r="T154" s="5"/>
       <c r="U154" s="5"/>
@@ -13650,7 +13869,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R155" s="5"/>
+      <c r="R155" s="43"/>
       <c r="S155" s="5"/>
       <c r="T155" s="5"/>
       <c r="U155" s="5"/>
@@ -13716,7 +13935,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R156" s="5"/>
+      <c r="R156" s="43"/>
       <c r="S156" s="5"/>
       <c r="T156" s="5"/>
       <c r="U156" s="5"/>
@@ -13782,7 +14001,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R157" s="5"/>
+      <c r="R157" s="43"/>
       <c r="S157" s="5"/>
       <c r="T157" s="5"/>
       <c r="U157" s="5"/>
@@ -13848,7 +14067,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R158" s="5"/>
+      <c r="R158" s="43"/>
       <c r="S158" s="5"/>
       <c r="T158" s="5"/>
       <c r="U158" s="5"/>
@@ -13914,7 +14133,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R159" s="5"/>
+      <c r="R159" s="43"/>
       <c r="S159" s="5"/>
       <c r="T159" s="5"/>
       <c r="U159" s="5"/>
@@ -13980,7 +14199,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R160" s="5"/>
+      <c r="R160" s="43"/>
       <c r="S160" s="5"/>
       <c r="T160" s="5"/>
       <c r="U160" s="5"/>
@@ -14046,7 +14265,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R161" s="5"/>
+      <c r="R161" s="43"/>
       <c r="S161" s="5"/>
       <c r="T161" s="5"/>
       <c r="U161" s="5"/>
@@ -14112,7 +14331,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R162" s="5"/>
+      <c r="R162" s="43"/>
       <c r="S162" s="5"/>
       <c r="T162" s="5"/>
       <c r="U162" s="5"/>
@@ -14178,7 +14397,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R163" s="5"/>
+      <c r="R163" s="43"/>
       <c r="S163" s="5"/>
       <c r="T163" s="5"/>
       <c r="U163" s="5"/>
@@ -14244,7 +14463,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R164" s="5"/>
+      <c r="R164" s="43"/>
       <c r="S164" s="5"/>
       <c r="T164" s="5"/>
       <c r="U164" s="5"/>
@@ -14310,7 +14529,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R165" s="5"/>
+      <c r="R165" s="43"/>
       <c r="S165" s="5"/>
       <c r="T165" s="5"/>
       <c r="U165" s="5"/>
@@ -14376,7 +14595,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R166" s="5"/>
+      <c r="R166" s="43"/>
       <c r="S166" s="5"/>
       <c r="T166" s="5"/>
       <c r="U166" s="5"/>
@@ -14442,7 +14661,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R167" s="5"/>
+      <c r="R167" s="43"/>
       <c r="S167" s="5"/>
       <c r="T167" s="5"/>
       <c r="U167" s="5"/>
@@ -14508,7 +14727,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R168" s="5"/>
+      <c r="R168" s="43"/>
       <c r="S168" s="5"/>
       <c r="T168" s="5"/>
       <c r="U168" s="5"/>
@@ -14574,7 +14793,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R169" s="5"/>
+      <c r="R169" s="43"/>
       <c r="S169" s="5"/>
       <c r="T169" s="5"/>
       <c r="U169" s="5"/>
@@ -14640,7 +14859,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R170" s="5"/>
+      <c r="R170" s="43"/>
       <c r="S170" s="5"/>
       <c r="T170" s="5"/>
       <c r="U170" s="5"/>
@@ -14706,7 +14925,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R171" s="5"/>
+      <c r="R171" s="43"/>
       <c r="S171" s="5"/>
       <c r="T171" s="5"/>
       <c r="U171" s="5"/>
@@ -14772,7 +14991,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R172" s="5"/>
+      <c r="R172" s="43"/>
       <c r="S172" s="5"/>
       <c r="T172" s="5"/>
       <c r="U172" s="5"/>
@@ -14838,7 +15057,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R173" s="5"/>
+      <c r="R173" s="43"/>
       <c r="S173" s="5"/>
       <c r="T173" s="5"/>
       <c r="U173" s="5"/>
@@ -14904,7 +15123,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R174" s="5"/>
+      <c r="R174" s="43"/>
       <c r="S174" s="5"/>
       <c r="T174" s="5"/>
       <c r="U174" s="5"/>
@@ -14970,7 +15189,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R175" s="5"/>
+      <c r="R175" s="43"/>
       <c r="S175" s="5"/>
       <c r="T175" s="5"/>
       <c r="U175" s="5"/>
@@ -15036,7 +15255,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R176" s="5"/>
+      <c r="R176" s="43"/>
       <c r="S176" s="5"/>
       <c r="T176" s="5"/>
       <c r="U176" s="5"/>
@@ -15102,7 +15321,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R177" s="5"/>
+      <c r="R177" s="43"/>
       <c r="S177" s="5"/>
       <c r="T177" s="5"/>
       <c r="U177" s="5"/>
@@ -15168,7 +15387,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R178" s="5"/>
+      <c r="R178" s="43"/>
       <c r="S178" s="5"/>
       <c r="T178" s="5"/>
       <c r="U178" s="5"/>
@@ -15234,7 +15453,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R179" s="5"/>
+      <c r="R179" s="43"/>
       <c r="S179" s="5"/>
       <c r="T179" s="5"/>
       <c r="U179" s="5"/>
@@ -15300,7 +15519,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R180" s="5"/>
+      <c r="R180" s="43"/>
       <c r="S180" s="5"/>
       <c r="T180" s="5"/>
       <c r="U180" s="5"/>
@@ -15366,7 +15585,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R181" s="5"/>
+      <c r="R181" s="43"/>
       <c r="S181" s="5"/>
       <c r="T181" s="5"/>
       <c r="U181" s="5"/>
@@ -15432,7 +15651,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R182" s="5"/>
+      <c r="R182" s="43"/>
       <c r="S182" s="5"/>
       <c r="T182" s="5"/>
       <c r="U182" s="5"/>
@@ -15498,7 +15717,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R183" s="5"/>
+      <c r="R183" s="43"/>
       <c r="S183" s="5"/>
       <c r="T183" s="5"/>
       <c r="U183" s="5"/>
@@ -15564,7 +15783,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R184" s="5"/>
+      <c r="R184" s="43"/>
       <c r="S184" s="5"/>
       <c r="T184" s="5"/>
       <c r="U184" s="5"/>
@@ -15630,7 +15849,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R185" s="5"/>
+      <c r="R185" s="43"/>
       <c r="S185" s="5"/>
       <c r="T185" s="5"/>
       <c r="U185" s="5"/>
@@ -15696,7 +15915,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R186" s="5"/>
+      <c r="R186" s="43"/>
       <c r="S186" s="5"/>
       <c r="T186" s="5"/>
       <c r="U186" s="5"/>
@@ -15762,7 +15981,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R187" s="5"/>
+      <c r="R187" s="43"/>
       <c r="S187" s="5"/>
       <c r="T187" s="5"/>
       <c r="U187" s="5"/>
@@ -15828,7 +16047,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R188" s="5"/>
+      <c r="R188" s="43"/>
       <c r="S188" s="5"/>
       <c r="T188" s="5"/>
       <c r="U188" s="5"/>
@@ -15894,7 +16113,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R189" s="5"/>
+      <c r="R189" s="43"/>
       <c r="S189" s="5"/>
       <c r="T189" s="5"/>
       <c r="U189" s="5"/>
@@ -15960,7 +16179,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R190" s="5"/>
+      <c r="R190" s="43"/>
       <c r="S190" s="5"/>
       <c r="T190" s="5"/>
       <c r="U190" s="5"/>
@@ -16026,7 +16245,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R191" s="5"/>
+      <c r="R191" s="43"/>
       <c r="S191" s="5"/>
       <c r="T191" s="5"/>
       <c r="U191" s="5"/>
@@ -16092,7 +16311,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R192" s="5"/>
+      <c r="R192" s="43"/>
       <c r="S192" s="5"/>
       <c r="T192" s="5"/>
       <c r="U192" s="5"/>
@@ -16158,7 +16377,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R193" s="5"/>
+      <c r="R193" s="43"/>
       <c r="S193" s="5"/>
       <c r="T193" s="5"/>
       <c r="U193" s="5"/>
@@ -16224,7 +16443,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R194" s="5"/>
+      <c r="R194" s="43"/>
       <c r="S194" s="5"/>
       <c r="T194" s="5"/>
       <c r="U194" s="5"/>
@@ -16290,7 +16509,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R195" s="5"/>
+      <c r="R195" s="43"/>
       <c r="S195" s="5"/>
       <c r="T195" s="5"/>
       <c r="U195" s="5"/>
@@ -16356,7 +16575,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R196" s="5"/>
+      <c r="R196" s="43"/>
       <c r="S196" s="5"/>
       <c r="T196" s="5"/>
       <c r="U196" s="5"/>
@@ -16422,7 +16641,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R197" s="5"/>
+      <c r="R197" s="43"/>
       <c r="S197" s="5"/>
       <c r="T197" s="5"/>
       <c r="U197" s="5"/>
@@ -16488,7 +16707,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R198" s="5"/>
+      <c r="R198" s="43"/>
       <c r="S198" s="5"/>
       <c r="T198" s="5"/>
       <c r="U198" s="5"/>
@@ -16554,7 +16773,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R199" s="5"/>
+      <c r="R199" s="43"/>
       <c r="S199" s="5"/>
       <c r="T199" s="5"/>
       <c r="U199" s="5"/>
@@ -16620,7 +16839,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R200" s="5"/>
+      <c r="R200" s="43"/>
       <c r="S200" s="5"/>
       <c r="T200" s="5"/>
       <c r="U200" s="5"/>
@@ -16686,7 +16905,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R201" s="5"/>
+      <c r="R201" s="43"/>
       <c r="S201" s="5"/>
       <c r="T201" s="5"/>
       <c r="U201" s="5"/>
@@ -16752,7 +16971,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R202" s="5"/>
+      <c r="R202" s="43"/>
       <c r="S202" s="5"/>
       <c r="T202" s="5"/>
       <c r="U202" s="5"/>
@@ -16818,7 +17037,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R203" s="5"/>
+      <c r="R203" s="43"/>
       <c r="S203" s="5"/>
       <c r="T203" s="5"/>
       <c r="U203" s="5"/>
@@ -16884,7 +17103,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R204" s="5"/>
+      <c r="R204" s="43"/>
       <c r="S204" s="5"/>
       <c r="T204" s="5"/>
       <c r="U204" s="5"/>
@@ -16950,7 +17169,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R205" s="5"/>
+      <c r="R205" s="43"/>
       <c r="S205" s="5"/>
       <c r="T205" s="5"/>
       <c r="U205" s="5"/>
@@ -17016,7 +17235,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R206" s="5"/>
+      <c r="R206" s="43"/>
       <c r="S206" s="5"/>
       <c r="T206" s="5"/>
       <c r="U206" s="5"/>
@@ -17082,7 +17301,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R207" s="5"/>
+      <c r="R207" s="43"/>
       <c r="S207" s="5"/>
       <c r="T207" s="5"/>
       <c r="U207" s="5"/>
@@ -17148,7 +17367,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R208" s="5"/>
+      <c r="R208" s="43"/>
       <c r="S208" s="5"/>
       <c r="T208" s="5"/>
       <c r="U208" s="5"/>
@@ -17214,7 +17433,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R209" s="5"/>
+      <c r="R209" s="43"/>
       <c r="S209" s="5"/>
       <c r="T209" s="5"/>
       <c r="U209" s="5"/>
@@ -17280,7 +17499,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R210" s="5"/>
+      <c r="R210" s="43"/>
       <c r="S210" s="5"/>
       <c r="T210" s="5"/>
       <c r="U210" s="5"/>
@@ -17346,7 +17565,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R211" s="5"/>
+      <c r="R211" s="43"/>
       <c r="S211" s="5"/>
       <c r="T211" s="5"/>
       <c r="U211" s="5"/>
@@ -17412,7 +17631,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R212" s="5"/>
+      <c r="R212" s="43"/>
       <c r="S212" s="5"/>
       <c r="T212" s="5"/>
       <c r="U212" s="5"/>
@@ -17478,7 +17697,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R213" s="5"/>
+      <c r="R213" s="43"/>
       <c r="S213" s="5"/>
       <c r="T213" s="5"/>
       <c r="U213" s="5"/>
@@ -17544,7 +17763,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R214" s="5"/>
+      <c r="R214" s="43"/>
       <c r="S214" s="5"/>
       <c r="T214" s="5"/>
       <c r="U214" s="5"/>
@@ -17610,7 +17829,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R215" s="5"/>
+      <c r="R215" s="43"/>
       <c r="S215" s="5"/>
       <c r="T215" s="5"/>
       <c r="U215" s="5"/>
@@ -17676,7 +17895,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R216" s="5"/>
+      <c r="R216" s="43"/>
       <c r="S216" s="5"/>
       <c r="T216" s="5"/>
       <c r="U216" s="5"/>
@@ -17742,7 +17961,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R217" s="5"/>
+      <c r="R217" s="43"/>
       <c r="S217" s="5"/>
       <c r="T217" s="5"/>
       <c r="U217" s="5"/>
@@ -17808,7 +18027,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R218" s="5"/>
+      <c r="R218" s="43"/>
       <c r="S218" s="5"/>
       <c r="T218" s="5"/>
       <c r="U218" s="5"/>
@@ -17874,7 +18093,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R219" s="5"/>
+      <c r="R219" s="43"/>
       <c r="S219" s="5"/>
       <c r="T219" s="5"/>
       <c r="U219" s="5"/>
@@ -17940,7 +18159,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R220" s="5"/>
+      <c r="R220" s="43"/>
       <c r="S220" s="5"/>
       <c r="T220" s="5"/>
       <c r="U220" s="5"/>
@@ -18006,7 +18225,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R221" s="5"/>
+      <c r="R221" s="43"/>
       <c r="S221" s="5"/>
       <c r="T221" s="5"/>
       <c r="U221" s="5"/>
@@ -18072,7 +18291,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R222" s="5"/>
+      <c r="R222" s="43"/>
       <c r="S222" s="5"/>
       <c r="T222" s="5"/>
       <c r="U222" s="5"/>
@@ -18138,7 +18357,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R223" s="5"/>
+      <c r="R223" s="43"/>
       <c r="S223" s="5"/>
       <c r="T223" s="5"/>
       <c r="U223" s="5"/>
@@ -18204,7 +18423,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R224" s="5"/>
+      <c r="R224" s="43"/>
       <c r="S224" s="5"/>
       <c r="T224" s="5"/>
       <c r="U224" s="5"/>
@@ -18270,7 +18489,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R225" s="5"/>
+      <c r="R225" s="43"/>
       <c r="S225" s="5"/>
       <c r="T225" s="5"/>
       <c r="U225" s="5"/>
@@ -18336,7 +18555,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R226" s="5"/>
+      <c r="R226" s="43"/>
       <c r="S226" s="5"/>
       <c r="T226" s="5"/>
       <c r="U226" s="5"/>
@@ -18402,7 +18621,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R227" s="5"/>
+      <c r="R227" s="43"/>
       <c r="S227" s="5"/>
       <c r="T227" s="5"/>
       <c r="U227" s="5"/>
@@ -18468,7 +18687,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R228" s="5"/>
+      <c r="R228" s="43"/>
       <c r="S228" s="5"/>
       <c r="T228" s="5"/>
       <c r="U228" s="5"/>
@@ -18534,7 +18753,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R229" s="5"/>
+      <c r="R229" s="43"/>
       <c r="S229" s="5"/>
       <c r="T229" s="5"/>
       <c r="U229" s="5"/>
@@ -18600,7 +18819,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R230" s="5"/>
+      <c r="R230" s="43"/>
       <c r="S230" s="5"/>
       <c r="T230" s="5"/>
       <c r="U230" s="5"/>
@@ -18666,7 +18885,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R231" s="5"/>
+      <c r="R231" s="43"/>
       <c r="S231" s="5"/>
       <c r="T231" s="5"/>
       <c r="U231" s="5"/>
@@ -18732,7 +18951,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R232" s="5"/>
+      <c r="R232" s="43"/>
       <c r="S232" s="5"/>
       <c r="T232" s="5"/>
       <c r="U232" s="5"/>
@@ -18798,7 +19017,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R233" s="5"/>
+      <c r="R233" s="43"/>
       <c r="S233" s="5"/>
       <c r="T233" s="5"/>
       <c r="U233" s="5"/>
@@ -18864,7 +19083,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R234" s="5"/>
+      <c r="R234" s="43"/>
       <c r="S234" s="5"/>
       <c r="T234" s="5"/>
       <c r="U234" s="5"/>
@@ -18930,7 +19149,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R235" s="5"/>
+      <c r="R235" s="43"/>
       <c r="S235" s="5"/>
       <c r="T235" s="5"/>
       <c r="U235" s="5"/>
@@ -18996,7 +19215,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R236" s="5"/>
+      <c r="R236" s="43"/>
       <c r="S236" s="5"/>
       <c r="T236" s="5"/>
       <c r="U236" s="5"/>
@@ -19062,7 +19281,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R237" s="5"/>
+      <c r="R237" s="43"/>
       <c r="S237" s="5"/>
       <c r="T237" s="5"/>
       <c r="U237" s="5"/>
@@ -19128,7 +19347,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R238" s="5"/>
+      <c r="R238" s="43"/>
       <c r="S238" s="5"/>
       <c r="T238" s="5"/>
       <c r="U238" s="5"/>
@@ -19194,7 +19413,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R239" s="5"/>
+      <c r="R239" s="43"/>
       <c r="S239" s="5"/>
       <c r="T239" s="5"/>
       <c r="U239" s="5"/>
@@ -19260,7 +19479,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R240" s="5"/>
+      <c r="R240" s="43"/>
       <c r="S240" s="5"/>
       <c r="T240" s="5"/>
       <c r="U240" s="5"/>
@@ -19326,7 +19545,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R241" s="5"/>
+      <c r="R241" s="43"/>
       <c r="S241" s="5"/>
       <c r="T241" s="5"/>
       <c r="U241" s="5"/>
@@ -19392,7 +19611,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R242" s="5"/>
+      <c r="R242" s="43"/>
       <c r="S242" s="5"/>
       <c r="T242" s="5"/>
       <c r="U242" s="5"/>
@@ -19458,7 +19677,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R243" s="5"/>
+      <c r="R243" s="43"/>
       <c r="S243" s="5"/>
       <c r="T243" s="5"/>
       <c r="U243" s="5"/>
@@ -19524,7 +19743,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R244" s="5"/>
+      <c r="R244" s="43"/>
       <c r="S244" s="5"/>
       <c r="T244" s="5"/>
       <c r="U244" s="5"/>
@@ -19590,7 +19809,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R245" s="5"/>
+      <c r="R245" s="43"/>
       <c r="S245" s="5"/>
       <c r="T245" s="5"/>
       <c r="U245" s="5"/>
@@ -19656,7 +19875,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R246" s="5"/>
+      <c r="R246" s="43"/>
       <c r="S246" s="5"/>
       <c r="T246" s="5"/>
       <c r="U246" s="5"/>
@@ -19722,7 +19941,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R247" s="5"/>
+      <c r="R247" s="43"/>
       <c r="S247" s="5"/>
       <c r="T247" s="5"/>
       <c r="U247" s="5"/>
@@ -19788,7 +20007,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R248" s="5"/>
+      <c r="R248" s="43"/>
       <c r="S248" s="5"/>
       <c r="T248" s="5"/>
       <c r="U248" s="5"/>
@@ -19854,7 +20073,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R249" s="5"/>
+      <c r="R249" s="43"/>
       <c r="S249" s="5"/>
       <c r="T249" s="5"/>
       <c r="U249" s="5"/>
@@ -19920,7 +20139,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R250" s="5"/>
+      <c r="R250" s="43"/>
       <c r="S250" s="5"/>
       <c r="T250" s="5"/>
       <c r="U250" s="5"/>
@@ -19986,7 +20205,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R251" s="5"/>
+      <c r="R251" s="43"/>
       <c r="S251" s="5"/>
       <c r="T251" s="5"/>
       <c r="U251" s="5"/>
@@ -20052,7 +20271,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R252" s="5"/>
+      <c r="R252" s="43"/>
       <c r="S252" s="5"/>
       <c r="T252" s="5"/>
       <c r="U252" s="5"/>
@@ -20118,7 +20337,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R253" s="5"/>
+      <c r="R253" s="43"/>
       <c r="S253" s="5"/>
       <c r="T253" s="5"/>
       <c r="U253" s="5"/>
@@ -20184,7 +20403,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R254" s="5"/>
+      <c r="R254" s="43"/>
       <c r="S254" s="5"/>
       <c r="T254" s="5"/>
       <c r="U254" s="5"/>
@@ -20250,7 +20469,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R255" s="5"/>
+      <c r="R255" s="43"/>
       <c r="S255" s="5"/>
       <c r="T255" s="5"/>
       <c r="U255" s="5"/>
@@ -20316,7 +20535,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R256" s="5"/>
+      <c r="R256" s="43"/>
       <c r="S256" s="5"/>
       <c r="T256" s="5"/>
       <c r="U256" s="5"/>
@@ -20382,7 +20601,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R257" s="5"/>
+      <c r="R257" s="43"/>
       <c r="S257" s="5"/>
       <c r="T257" s="5"/>
       <c r="U257" s="5"/>
@@ -20448,7 +20667,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R258" s="5"/>
+      <c r="R258" s="43"/>
       <c r="S258" s="5"/>
       <c r="T258" s="5"/>
       <c r="U258" s="5"/>
@@ -20514,7 +20733,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R259" s="5"/>
+      <c r="R259" s="43"/>
       <c r="S259" s="5"/>
       <c r="T259" s="5"/>
       <c r="U259" s="5"/>
@@ -20580,7 +20799,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R260" s="5"/>
+      <c r="R260" s="43"/>
       <c r="S260" s="5"/>
       <c r="T260" s="5"/>
       <c r="U260" s="5"/>
@@ -20646,7 +20865,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R261" s="5"/>
+      <c r="R261" s="43"/>
       <c r="S261" s="5"/>
       <c r="T261" s="5"/>
       <c r="U261" s="5"/>
@@ -20712,7 +20931,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R262" s="5"/>
+      <c r="R262" s="43"/>
       <c r="S262" s="5"/>
       <c r="T262" s="5"/>
       <c r="U262" s="5"/>
@@ -20778,7 +20997,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R263" s="5"/>
+      <c r="R263" s="43"/>
       <c r="S263" s="5"/>
       <c r="T263" s="5"/>
       <c r="U263" s="5"/>
@@ -20844,7 +21063,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R264" s="5"/>
+      <c r="R264" s="43"/>
       <c r="S264" s="5"/>
       <c r="T264" s="5"/>
       <c r="U264" s="5"/>
@@ -20910,7 +21129,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R265" s="5"/>
+      <c r="R265" s="43"/>
       <c r="S265" s="5"/>
       <c r="T265" s="5"/>
       <c r="U265" s="5"/>
@@ -20976,7 +21195,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R266" s="5"/>
+      <c r="R266" s="43"/>
       <c r="S266" s="5"/>
       <c r="T266" s="5"/>
       <c r="U266" s="5"/>
@@ -21042,7 +21261,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R267" s="5"/>
+      <c r="R267" s="43"/>
       <c r="S267" s="5"/>
       <c r="T267" s="5"/>
       <c r="U267" s="5"/>
@@ -21108,7 +21327,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R268" s="5"/>
+      <c r="R268" s="43"/>
       <c r="S268" s="5"/>
       <c r="T268" s="5"/>
       <c r="U268" s="5"/>
@@ -21174,7 +21393,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R269" s="5"/>
+      <c r="R269" s="43"/>
       <c r="S269" s="5"/>
       <c r="T269" s="5"/>
       <c r="U269" s="5"/>
@@ -21240,7 +21459,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R270" s="5"/>
+      <c r="R270" s="43"/>
       <c r="S270" s="5"/>
       <c r="T270" s="5"/>
       <c r="U270" s="5"/>
@@ -21306,7 +21525,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R271" s="5"/>
+      <c r="R271" s="43"/>
       <c r="S271" s="5"/>
       <c r="T271" s="5"/>
       <c r="U271" s="5"/>
@@ -21372,7 +21591,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R272" s="5"/>
+      <c r="R272" s="43"/>
       <c r="S272" s="5"/>
       <c r="T272" s="5"/>
       <c r="U272" s="5"/>
@@ -21438,7 +21657,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R273" s="5"/>
+      <c r="R273" s="43"/>
       <c r="S273" s="5"/>
       <c r="T273" s="5"/>
       <c r="U273" s="5"/>
@@ -21504,7 +21723,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R274" s="5"/>
+      <c r="R274" s="43"/>
       <c r="S274" s="5"/>
       <c r="T274" s="5"/>
       <c r="U274" s="5"/>
@@ -21570,7 +21789,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R275" s="5"/>
+      <c r="R275" s="43"/>
       <c r="S275" s="5"/>
       <c r="T275" s="5"/>
       <c r="U275" s="5"/>
@@ -21636,7 +21855,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R276" s="5"/>
+      <c r="R276" s="43"/>
       <c r="S276" s="5"/>
       <c r="T276" s="5"/>
       <c r="U276" s="5"/>
@@ -21702,7 +21921,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R277" s="5"/>
+      <c r="R277" s="43"/>
       <c r="S277" s="5"/>
       <c r="T277" s="5"/>
       <c r="U277" s="5"/>
@@ -21768,7 +21987,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R278" s="5"/>
+      <c r="R278" s="43"/>
       <c r="S278" s="5"/>
       <c r="T278" s="5"/>
       <c r="U278" s="5"/>
@@ -21834,7 +22053,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R279" s="5"/>
+      <c r="R279" s="43"/>
       <c r="S279" s="5"/>
       <c r="T279" s="5"/>
       <c r="U279" s="5"/>
@@ -21900,7 +22119,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R280" s="5"/>
+      <c r="R280" s="43"/>
       <c r="S280" s="5"/>
       <c r="T280" s="5"/>
       <c r="U280" s="5"/>
@@ -21966,7 +22185,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R281" s="5"/>
+      <c r="R281" s="43"/>
       <c r="S281" s="5"/>
       <c r="T281" s="5"/>
       <c r="U281" s="5"/>
@@ -22032,7 +22251,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R282" s="5"/>
+      <c r="R282" s="43"/>
       <c r="S282" s="5"/>
       <c r="T282" s="5"/>
       <c r="U282" s="5"/>
@@ -22098,7 +22317,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R283" s="5"/>
+      <c r="R283" s="43"/>
       <c r="S283" s="5"/>
       <c r="T283" s="5"/>
       <c r="U283" s="5"/>
@@ -22164,7 +22383,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R284" s="5"/>
+      <c r="R284" s="43"/>
       <c r="S284" s="5"/>
       <c r="T284" s="5"/>
       <c r="U284" s="5"/>
@@ -22230,7 +22449,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R285" s="5"/>
+      <c r="R285" s="43"/>
       <c r="S285" s="5"/>
       <c r="T285" s="5"/>
       <c r="U285" s="5"/>
@@ -22296,7 +22515,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R286" s="5"/>
+      <c r="R286" s="43"/>
       <c r="S286" s="5"/>
       <c r="T286" s="5"/>
       <c r="U286" s="5"/>
@@ -22362,7 +22581,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R287" s="5"/>
+      <c r="R287" s="43"/>
       <c r="S287" s="5"/>
       <c r="T287" s="5"/>
       <c r="U287" s="5"/>
@@ -22428,7 +22647,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R288" s="5"/>
+      <c r="R288" s="43"/>
       <c r="S288" s="5"/>
       <c r="T288" s="5"/>
       <c r="U288" s="5"/>
@@ -22494,7 +22713,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R289" s="5"/>
+      <c r="R289" s="43"/>
       <c r="S289" s="5"/>
       <c r="T289" s="5"/>
       <c r="U289" s="5"/>
@@ -22560,7 +22779,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R290" s="5"/>
+      <c r="R290" s="43"/>
       <c r="S290" s="5"/>
       <c r="T290" s="5"/>
       <c r="U290" s="5"/>
@@ -22626,7 +22845,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R291" s="5"/>
+      <c r="R291" s="43"/>
       <c r="S291" s="5"/>
       <c r="T291" s="5"/>
       <c r="U291" s="5"/>
@@ -22692,7 +22911,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R292" s="5"/>
+      <c r="R292" s="43"/>
       <c r="S292" s="5"/>
       <c r="T292" s="5"/>
       <c r="U292" s="5"/>
@@ -22758,7 +22977,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R293" s="5"/>
+      <c r="R293" s="43"/>
       <c r="S293" s="5"/>
       <c r="T293" s="5"/>
       <c r="U293" s="5"/>
@@ -22824,7 +23043,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R294" s="5"/>
+      <c r="R294" s="43"/>
       <c r="S294" s="5"/>
       <c r="T294" s="5"/>
       <c r="U294" s="5"/>
@@ -22890,7 +23109,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R295" s="5"/>
+      <c r="R295" s="43"/>
       <c r="S295" s="5"/>
       <c r="T295" s="5"/>
       <c r="U295" s="5"/>
@@ -22956,7 +23175,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R296" s="5"/>
+      <c r="R296" s="43"/>
       <c r="S296" s="5"/>
       <c r="T296" s="5"/>
       <c r="U296" s="5"/>
@@ -23022,7 +23241,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R297" s="5"/>
+      <c r="R297" s="43"/>
       <c r="S297" s="5"/>
       <c r="T297" s="5"/>
       <c r="U297" s="5"/>
@@ -23088,7 +23307,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R298" s="5"/>
+      <c r="R298" s="43"/>
       <c r="S298" s="5"/>
       <c r="T298" s="5"/>
       <c r="U298" s="5"/>
@@ -23154,7 +23373,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R299" s="5"/>
+      <c r="R299" s="43"/>
       <c r="S299" s="5"/>
       <c r="T299" s="5"/>
       <c r="U299" s="5"/>
@@ -23220,7 +23439,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R300" s="5"/>
+      <c r="R300" s="43"/>
       <c r="S300" s="5"/>
       <c r="T300" s="5"/>
       <c r="U300" s="5"/>
@@ -23286,7 +23505,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R301" s="5"/>
+      <c r="R301" s="43"/>
       <c r="S301" s="5"/>
       <c r="T301" s="5"/>
       <c r="U301" s="5"/>
@@ -23352,7 +23571,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R302" s="5"/>
+      <c r="R302" s="43"/>
       <c r="S302" s="5"/>
       <c r="T302" s="5"/>
       <c r="U302" s="5"/>
@@ -23418,7 +23637,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R303" s="5"/>
+      <c r="R303" s="43"/>
       <c r="S303" s="5"/>
       <c r="T303" s="5"/>
       <c r="U303" s="5"/>
@@ -23484,7 +23703,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R304" s="5"/>
+      <c r="R304" s="43"/>
       <c r="S304" s="5"/>
       <c r="T304" s="5"/>
       <c r="U304" s="5"/>
@@ -23550,7 +23769,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R305" s="5"/>
+      <c r="R305" s="43"/>
       <c r="S305" s="5"/>
       <c r="T305" s="5"/>
       <c r="U305" s="5"/>
@@ -23616,7 +23835,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R306" s="5"/>
+      <c r="R306" s="43"/>
       <c r="S306" s="5"/>
       <c r="T306" s="5"/>
       <c r="U306" s="5"/>
@@ -23682,7 +23901,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R307" s="5"/>
+      <c r="R307" s="43"/>
       <c r="S307" s="5"/>
       <c r="T307" s="5"/>
       <c r="U307" s="5"/>
@@ -23748,7 +23967,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R308" s="5"/>
+      <c r="R308" s="43"/>
       <c r="S308" s="5"/>
       <c r="T308" s="5"/>
       <c r="U308" s="5"/>
@@ -23814,7 +24033,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R309" s="5"/>
+      <c r="R309" s="43"/>
       <c r="S309" s="5"/>
       <c r="T309" s="5"/>
       <c r="U309" s="5"/>
@@ -23880,7 +24099,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R310" s="5"/>
+      <c r="R310" s="43"/>
       <c r="S310" s="5"/>
       <c r="T310" s="5"/>
       <c r="U310" s="5"/>
@@ -23946,7 +24165,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R311" s="5"/>
+      <c r="R311" s="43"/>
       <c r="S311" s="5"/>
       <c r="T311" s="5"/>
       <c r="U311" s="5"/>
@@ -24012,7 +24231,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R312" s="5"/>
+      <c r="R312" s="43"/>
       <c r="S312" s="5"/>
       <c r="T312" s="5"/>
       <c r="U312" s="5"/>
@@ -24078,7 +24297,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R313" s="5"/>
+      <c r="R313" s="43"/>
       <c r="S313" s="5"/>
       <c r="T313" s="5"/>
       <c r="U313" s="5"/>
@@ -24144,7 +24363,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R314" s="5"/>
+      <c r="R314" s="43"/>
       <c r="S314" s="5"/>
       <c r="T314" s="5"/>
       <c r="U314" s="5"/>
@@ -24210,7 +24429,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R315" s="5"/>
+      <c r="R315" s="43"/>
       <c r="S315" s="5"/>
       <c r="T315" s="5"/>
       <c r="U315" s="5"/>
@@ -24276,7 +24495,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R316" s="5"/>
+      <c r="R316" s="43"/>
       <c r="S316" s="5"/>
       <c r="T316" s="5"/>
       <c r="U316" s="5"/>
@@ -24342,7 +24561,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R317" s="5"/>
+      <c r="R317" s="43"/>
       <c r="S317" s="5"/>
       <c r="T317" s="5"/>
       <c r="U317" s="5"/>
@@ -24408,7 +24627,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R318" s="5"/>
+      <c r="R318" s="43"/>
       <c r="S318" s="5"/>
       <c r="T318" s="5"/>
       <c r="U318" s="5"/>
@@ -24474,7 +24693,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R319" s="5"/>
+      <c r="R319" s="43"/>
       <c r="S319" s="5"/>
       <c r="T319" s="5"/>
       <c r="U319" s="5"/>
@@ -24540,7 +24759,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R320" s="5"/>
+      <c r="R320" s="43"/>
       <c r="S320" s="5"/>
       <c r="T320" s="5"/>
       <c r="U320" s="5"/>
@@ -24606,7 +24825,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R321" s="5"/>
+      <c r="R321" s="43"/>
       <c r="S321" s="5"/>
       <c r="T321" s="5"/>
       <c r="U321" s="5"/>
@@ -24672,7 +24891,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R322" s="5"/>
+      <c r="R322" s="43"/>
       <c r="S322" s="5"/>
       <c r="T322" s="5"/>
       <c r="U322" s="5"/>
@@ -24738,7 +24957,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R323" s="5"/>
+      <c r="R323" s="43"/>
       <c r="S323" s="5"/>
       <c r="T323" s="5"/>
       <c r="U323" s="5"/>
@@ -24804,7 +25023,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R324" s="5"/>
+      <c r="R324" s="43"/>
       <c r="S324" s="5"/>
       <c r="T324" s="5"/>
       <c r="U324" s="5"/>
@@ -24870,7 +25089,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R325" s="5"/>
+      <c r="R325" s="43"/>
       <c r="S325" s="5"/>
       <c r="T325" s="5"/>
       <c r="U325" s="5"/>
@@ -24936,7 +25155,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R326" s="5"/>
+      <c r="R326" s="43"/>
       <c r="S326" s="5"/>
       <c r="T326" s="5"/>
       <c r="U326" s="5"/>
@@ -25002,7 +25221,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R327" s="5"/>
+      <c r="R327" s="43"/>
       <c r="S327" s="5"/>
       <c r="T327" s="5"/>
       <c r="U327" s="5"/>
@@ -25068,7 +25287,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R328" s="5"/>
+      <c r="R328" s="43"/>
       <c r="S328" s="5"/>
       <c r="T328" s="5"/>
       <c r="U328" s="5"/>
@@ -25134,7 +25353,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R329" s="5"/>
+      <c r="R329" s="43"/>
       <c r="S329" s="5"/>
       <c r="T329" s="5"/>
       <c r="U329" s="5"/>
@@ -25200,7 +25419,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R330" s="5"/>
+      <c r="R330" s="43"/>
       <c r="S330" s="5"/>
       <c r="T330" s="5"/>
       <c r="U330" s="5"/>
@@ -25266,7 +25485,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R331" s="5"/>
+      <c r="R331" s="43"/>
       <c r="S331" s="5"/>
       <c r="T331" s="5"/>
       <c r="U331" s="5"/>
@@ -25332,7 +25551,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R332" s="5"/>
+      <c r="R332" s="43"/>
       <c r="S332" s="5"/>
       <c r="T332" s="5"/>
       <c r="U332" s="5"/>
@@ -25398,7 +25617,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R333" s="5"/>
+      <c r="R333" s="43"/>
       <c r="S333" s="5"/>
       <c r="T333" s="5"/>
       <c r="U333" s="5"/>
@@ -25464,7 +25683,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R334" s="5"/>
+      <c r="R334" s="43"/>
       <c r="S334" s="5"/>
       <c r="T334" s="5"/>
       <c r="U334" s="5"/>
@@ -25530,7 +25749,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R335" s="5"/>
+      <c r="R335" s="43"/>
       <c r="S335" s="5"/>
       <c r="T335" s="5"/>
       <c r="U335" s="5"/>
@@ -25596,7 +25815,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R336" s="5"/>
+      <c r="R336" s="43"/>
       <c r="S336" s="5"/>
       <c r="T336" s="5"/>
       <c r="U336" s="5"/>
@@ -25662,7 +25881,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R337" s="5"/>
+      <c r="R337" s="43"/>
       <c r="S337" s="5"/>
       <c r="T337" s="5"/>
       <c r="U337" s="5"/>
@@ -25728,7 +25947,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R338" s="5"/>
+      <c r="R338" s="43"/>
       <c r="S338" s="5"/>
       <c r="T338" s="5"/>
       <c r="U338" s="5"/>
@@ -25794,7 +26013,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R339" s="5"/>
+      <c r="R339" s="43"/>
       <c r="S339" s="5"/>
       <c r="T339" s="5"/>
       <c r="U339" s="5"/>
@@ -25860,7 +26079,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R340" s="5"/>
+      <c r="R340" s="43"/>
       <c r="S340" s="5"/>
       <c r="T340" s="5"/>
       <c r="U340" s="5"/>
@@ -25926,7 +26145,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R341" s="5"/>
+      <c r="R341" s="43"/>
       <c r="S341" s="5"/>
       <c r="T341" s="5"/>
       <c r="U341" s="5"/>
@@ -25992,7 +26211,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R342" s="5"/>
+      <c r="R342" s="43"/>
       <c r="S342" s="5"/>
       <c r="T342" s="5"/>
       <c r="U342" s="5"/>
@@ -26058,7 +26277,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R343" s="5"/>
+      <c r="R343" s="43"/>
       <c r="S343" s="5"/>
       <c r="T343" s="5"/>
       <c r="U343" s="5"/>
@@ -26124,7 +26343,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R344" s="5"/>
+      <c r="R344" s="43"/>
       <c r="S344" s="5"/>
       <c r="T344" s="5"/>
       <c r="U344" s="5"/>
@@ -26190,7 +26409,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R345" s="5"/>
+      <c r="R345" s="43"/>
       <c r="S345" s="5"/>
       <c r="T345" s="5"/>
       <c r="U345" s="5"/>
@@ -26256,7 +26475,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R346" s="5"/>
+      <c r="R346" s="43"/>
       <c r="S346" s="5"/>
       <c r="T346" s="5"/>
       <c r="U346" s="5"/>
@@ -26322,7 +26541,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R347" s="5"/>
+      <c r="R347" s="43"/>
       <c r="S347" s="5"/>
       <c r="T347" s="5"/>
       <c r="U347" s="5"/>
@@ -26388,7 +26607,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R348" s="5"/>
+      <c r="R348" s="43"/>
       <c r="S348" s="5"/>
       <c r="T348" s="5"/>
       <c r="U348" s="5"/>
@@ -26454,7 +26673,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R349" s="5"/>
+      <c r="R349" s="43"/>
       <c r="S349" s="5"/>
       <c r="T349" s="5"/>
       <c r="U349" s="5"/>
@@ -26520,7 +26739,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R350" s="5"/>
+      <c r="R350" s="43"/>
       <c r="S350" s="5"/>
       <c r="T350" s="5"/>
       <c r="U350" s="5"/>
@@ -26586,7 +26805,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R351" s="5"/>
+      <c r="R351" s="43"/>
       <c r="S351" s="5"/>
       <c r="T351" s="5"/>
       <c r="U351" s="5"/>
@@ -26652,7 +26871,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R352" s="5"/>
+      <c r="R352" s="43"/>
       <c r="S352" s="5"/>
       <c r="T352" s="5"/>
       <c r="U352" s="5"/>
@@ -26718,7 +26937,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R353" s="5"/>
+      <c r="R353" s="43"/>
       <c r="S353" s="5"/>
       <c r="T353" s="5"/>
       <c r="U353" s="5"/>
@@ -26784,7 +27003,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R354" s="5"/>
+      <c r="R354" s="43"/>
       <c r="S354" s="5"/>
       <c r="T354" s="5"/>
       <c r="U354" s="5"/>
@@ -26850,7 +27069,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R355" s="5"/>
+      <c r="R355" s="43"/>
       <c r="S355" s="5"/>
       <c r="T355" s="5"/>
       <c r="U355" s="5"/>
@@ -26916,7 +27135,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R356" s="5"/>
+      <c r="R356" s="43"/>
       <c r="S356" s="5"/>
       <c r="T356" s="5"/>
       <c r="U356" s="5"/>
@@ -26982,7 +27201,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R357" s="5"/>
+      <c r="R357" s="43"/>
       <c r="S357" s="5"/>
       <c r="T357" s="5"/>
       <c r="U357" s="5"/>
@@ -27048,7 +27267,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R358" s="5"/>
+      <c r="R358" s="43"/>
       <c r="S358" s="5"/>
       <c r="T358" s="5"/>
       <c r="U358" s="5"/>
@@ -27114,7 +27333,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R359" s="5"/>
+      <c r="R359" s="43"/>
       <c r="S359" s="5"/>
       <c r="T359" s="5"/>
       <c r="U359" s="5"/>
@@ -27180,7 +27399,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R360" s="5"/>
+      <c r="R360" s="43"/>
       <c r="S360" s="5"/>
       <c r="T360" s="5"/>
       <c r="U360" s="5"/>
@@ -27246,7 +27465,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R361" s="5"/>
+      <c r="R361" s="43"/>
       <c r="S361" s="5"/>
       <c r="T361" s="5"/>
       <c r="U361" s="5"/>
@@ -27312,7 +27531,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R362" s="5"/>
+      <c r="R362" s="43"/>
       <c r="S362" s="5"/>
       <c r="T362" s="5"/>
       <c r="U362" s="5"/>
@@ -27378,7 +27597,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R363" s="5"/>
+      <c r="R363" s="43"/>
       <c r="S363" s="5"/>
       <c r="T363" s="5"/>
       <c r="U363" s="5"/>
@@ -27444,7 +27663,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R364" s="5"/>
+      <c r="R364" s="43"/>
       <c r="S364" s="5"/>
       <c r="T364" s="5"/>
       <c r="U364" s="5"/>
@@ -27510,7 +27729,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R365" s="5"/>
+      <c r="R365" s="43"/>
       <c r="S365" s="5"/>
       <c r="T365" s="5"/>
       <c r="U365" s="5"/>
@@ -27576,7 +27795,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R366" s="5"/>
+      <c r="R366" s="43"/>
       <c r="S366" s="5"/>
       <c r="T366" s="5"/>
       <c r="U366" s="5"/>
@@ -27642,7 +27861,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R367" s="5"/>
+      <c r="R367" s="43"/>
       <c r="S367" s="5"/>
       <c r="T367" s="5"/>
       <c r="U367" s="5"/>
@@ -27708,7 +27927,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R368" s="5"/>
+      <c r="R368" s="43"/>
       <c r="S368" s="5"/>
       <c r="T368" s="5"/>
       <c r="U368" s="5"/>
@@ -27774,7 +27993,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R369" s="5"/>
+      <c r="R369" s="43"/>
       <c r="S369" s="5"/>
       <c r="T369" s="5"/>
       <c r="U369" s="5"/>
@@ -27840,7 +28059,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R370" s="5"/>
+      <c r="R370" s="43"/>
       <c r="S370" s="5"/>
       <c r="T370" s="5"/>
       <c r="U370" s="5"/>
@@ -27906,7 +28125,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R371" s="5"/>
+      <c r="R371" s="43"/>
       <c r="S371" s="5"/>
       <c r="T371" s="5"/>
       <c r="U371" s="5"/>
@@ -27972,7 +28191,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R372" s="5"/>
+      <c r="R372" s="43"/>
       <c r="S372" s="5"/>
       <c r="T372" s="5"/>
       <c r="U372" s="5"/>
@@ -28038,7 +28257,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R373" s="5"/>
+      <c r="R373" s="43"/>
       <c r="S373" s="5"/>
       <c r="T373" s="5"/>
       <c r="U373" s="5"/>
@@ -28104,7 +28323,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R374" s="5"/>
+      <c r="R374" s="43"/>
       <c r="S374" s="5"/>
       <c r="T374" s="5"/>
       <c r="U374" s="5"/>
@@ -28170,7 +28389,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R375" s="5"/>
+      <c r="R375" s="43"/>
       <c r="S375" s="5"/>
       <c r="T375" s="5"/>
       <c r="U375" s="5"/>
@@ -28236,7 +28455,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R376" s="5"/>
+      <c r="R376" s="43"/>
       <c r="S376" s="5"/>
       <c r="T376" s="5"/>
       <c r="U376" s="5"/>
@@ -28302,7 +28521,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R377" s="5"/>
+      <c r="R377" s="43"/>
       <c r="S377" s="5"/>
       <c r="T377" s="5"/>
       <c r="U377" s="5"/>
@@ -28368,7 +28587,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R378" s="5"/>
+      <c r="R378" s="43"/>
       <c r="S378" s="5"/>
       <c r="T378" s="5"/>
       <c r="U378" s="5"/>
@@ -28434,7 +28653,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R379" s="5"/>
+      <c r="R379" s="43"/>
       <c r="S379" s="5"/>
       <c r="T379" s="5"/>
       <c r="U379" s="5"/>
@@ -28500,7 +28719,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R380" s="5"/>
+      <c r="R380" s="43"/>
       <c r="S380" s="5"/>
       <c r="T380" s="5"/>
       <c r="U380" s="5"/>
@@ -28566,7 +28785,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R381" s="5"/>
+      <c r="R381" s="43"/>
       <c r="S381" s="5"/>
       <c r="T381" s="5"/>
       <c r="U381" s="5"/>
@@ -28632,7 +28851,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R382" s="5"/>
+      <c r="R382" s="43"/>
       <c r="S382" s="5"/>
       <c r="T382" s="5"/>
       <c r="U382" s="5"/>
@@ -28698,7 +28917,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R383" s="5"/>
+      <c r="R383" s="43"/>
       <c r="S383" s="5"/>
       <c r="T383" s="5"/>
       <c r="U383" s="5"/>
@@ -28764,7 +28983,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R384" s="5"/>
+      <c r="R384" s="43"/>
       <c r="S384" s="5"/>
       <c r="T384" s="5"/>
       <c r="U384" s="5"/>
@@ -28830,7 +29049,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R385" s="5"/>
+      <c r="R385" s="43"/>
       <c r="S385" s="5"/>
       <c r="T385" s="5"/>
       <c r="U385" s="5"/>
@@ -28896,7 +29115,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R386" s="5"/>
+      <c r="R386" s="43"/>
       <c r="S386" s="5"/>
       <c r="T386" s="5"/>
       <c r="U386" s="5"/>
@@ -28962,7 +29181,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R387" s="5"/>
+      <c r="R387" s="43"/>
       <c r="S387" s="5"/>
       <c r="T387" s="5"/>
       <c r="U387" s="5"/>
@@ -29028,7 +29247,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R388" s="5"/>
+      <c r="R388" s="43"/>
       <c r="S388" s="5"/>
       <c r="T388" s="5"/>
       <c r="U388" s="5"/>
@@ -29094,7 +29313,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R389" s="5"/>
+      <c r="R389" s="43"/>
       <c r="S389" s="5"/>
       <c r="T389" s="5"/>
       <c r="U389" s="5"/>
@@ -29160,7 +29379,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R390" s="5"/>
+      <c r="R390" s="43"/>
       <c r="S390" s="5"/>
       <c r="T390" s="5"/>
       <c r="U390" s="5"/>
@@ -29226,7 +29445,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R391" s="5"/>
+      <c r="R391" s="43"/>
       <c r="S391" s="5"/>
       <c r="T391" s="5"/>
       <c r="U391" s="5"/>
@@ -29292,7 +29511,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R392" s="5"/>
+      <c r="R392" s="43"/>
       <c r="S392" s="5"/>
       <c r="T392" s="5"/>
       <c r="U392" s="5"/>
@@ -29358,7 +29577,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R393" s="5"/>
+      <c r="R393" s="43"/>
       <c r="S393" s="5"/>
       <c r="T393" s="5"/>
       <c r="U393" s="5"/>
@@ -29424,7 +29643,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R394" s="5"/>
+      <c r="R394" s="43"/>
       <c r="S394" s="5"/>
       <c r="T394" s="5"/>
       <c r="U394" s="5"/>
@@ -29490,7 +29709,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R395" s="5"/>
+      <c r="R395" s="43"/>
       <c r="S395" s="5"/>
       <c r="T395" s="5"/>
       <c r="U395" s="5"/>
@@ -29556,7 +29775,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R396" s="5"/>
+      <c r="R396" s="43"/>
       <c r="S396" s="5"/>
       <c r="T396" s="5"/>
       <c r="U396" s="5"/>
@@ -29622,7 +29841,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R397" s="5"/>
+      <c r="R397" s="43"/>
       <c r="S397" s="5"/>
       <c r="T397" s="5"/>
       <c r="U397" s="5"/>
@@ -29688,7 +29907,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R398" s="5"/>
+      <c r="R398" s="43"/>
       <c r="S398" s="5"/>
       <c r="T398" s="5"/>
       <c r="U398" s="5"/>
@@ -29754,7 +29973,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R399" s="5"/>
+      <c r="R399" s="43"/>
       <c r="S399" s="5"/>
       <c r="T399" s="5"/>
       <c r="U399" s="5"/>
@@ -29820,7 +30039,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R400" s="5"/>
+      <c r="R400" s="43"/>
       <c r="S400" s="5"/>
       <c r="T400" s="5"/>
       <c r="U400" s="5"/>
@@ -29886,7 +30105,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R401" s="5"/>
+      <c r="R401" s="43"/>
       <c r="S401" s="5"/>
       <c r="T401" s="5"/>
       <c r="U401" s="5"/>
@@ -29952,7 +30171,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R402" s="5"/>
+      <c r="R402" s="43"/>
       <c r="S402" s="5"/>
       <c r="T402" s="5"/>
       <c r="U402" s="5"/>
@@ -30018,7 +30237,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R403" s="5"/>
+      <c r="R403" s="43"/>
       <c r="S403" s="5"/>
       <c r="T403" s="5"/>
       <c r="U403" s="5"/>
@@ -30084,7 +30303,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R404" s="5"/>
+      <c r="R404" s="43"/>
       <c r="S404" s="5"/>
       <c r="T404" s="5"/>
       <c r="U404" s="5"/>
@@ -30150,7 +30369,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R405" s="5"/>
+      <c r="R405" s="43"/>
       <c r="S405" s="5"/>
       <c r="T405" s="5"/>
       <c r="U405" s="5"/>
@@ -30216,7 +30435,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R406" s="5"/>
+      <c r="R406" s="43"/>
       <c r="S406" s="5"/>
       <c r="T406" s="5"/>
       <c r="U406" s="5"/>
@@ -30282,7 +30501,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R407" s="5"/>
+      <c r="R407" s="43"/>
       <c r="S407" s="5"/>
       <c r="T407" s="5"/>
       <c r="U407" s="5"/>
@@ -30348,7 +30567,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R408" s="5"/>
+      <c r="R408" s="43"/>
       <c r="S408" s="5"/>
       <c r="T408" s="5"/>
       <c r="U408" s="5"/>
@@ -30414,7 +30633,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R409" s="5"/>
+      <c r="R409" s="43"/>
       <c r="S409" s="5"/>
       <c r="T409" s="5"/>
       <c r="U409" s="5"/>
@@ -30480,7 +30699,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R410" s="5"/>
+      <c r="R410" s="43"/>
       <c r="S410" s="5"/>
       <c r="T410" s="5"/>
       <c r="U410" s="5"/>
@@ -30546,7 +30765,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R411" s="5"/>
+      <c r="R411" s="43"/>
       <c r="S411" s="5"/>
       <c r="T411" s="5"/>
       <c r="U411" s="5"/>
@@ -30612,7 +30831,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R412" s="5"/>
+      <c r="R412" s="43"/>
       <c r="S412" s="5"/>
       <c r="T412" s="5"/>
       <c r="U412" s="5"/>
@@ -30678,7 +30897,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R413" s="5"/>
+      <c r="R413" s="43"/>
       <c r="S413" s="5"/>
       <c r="T413" s="5"/>
       <c r="U413" s="5"/>
@@ -30744,7 +30963,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R414" s="5"/>
+      <c r="R414" s="43"/>
       <c r="S414" s="5"/>
       <c r="T414" s="5"/>
       <c r="U414" s="5"/>
@@ -30810,7 +31029,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R415" s="5"/>
+      <c r="R415" s="43"/>
       <c r="S415" s="5"/>
       <c r="T415" s="5"/>
       <c r="U415" s="5"/>
@@ -30876,7 +31095,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R416" s="5"/>
+      <c r="R416" s="43"/>
       <c r="S416" s="5"/>
       <c r="T416" s="5"/>
       <c r="U416" s="5"/>
@@ -30942,7 +31161,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R417" s="5"/>
+      <c r="R417" s="43"/>
       <c r="S417" s="5"/>
       <c r="T417" s="5"/>
       <c r="U417" s="5"/>
@@ -31008,7 +31227,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R418" s="5"/>
+      <c r="R418" s="43"/>
       <c r="S418" s="5"/>
       <c r="T418" s="5"/>
       <c r="U418" s="5"/>
@@ -31074,7 +31293,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R419" s="5"/>
+      <c r="R419" s="43"/>
       <c r="S419" s="5"/>
       <c r="T419" s="5"/>
       <c r="U419" s="5"/>
@@ -31140,7 +31359,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R420" s="5"/>
+      <c r="R420" s="43"/>
       <c r="S420" s="5"/>
       <c r="T420" s="5"/>
       <c r="U420" s="5"/>
@@ -31206,7 +31425,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R421" s="5"/>
+      <c r="R421" s="43"/>
       <c r="S421" s="5"/>
       <c r="T421" s="5"/>
       <c r="U421" s="5"/>
@@ -31272,7 +31491,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R422" s="5"/>
+      <c r="R422" s="43"/>
       <c r="S422" s="5"/>
       <c r="T422" s="5"/>
       <c r="U422" s="5"/>
@@ -31338,7 +31557,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R423" s="5"/>
+      <c r="R423" s="43"/>
       <c r="S423" s="5"/>
       <c r="T423" s="5"/>
       <c r="U423" s="5"/>
@@ -31404,7 +31623,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R424" s="5"/>
+      <c r="R424" s="43"/>
       <c r="S424" s="5"/>
       <c r="T424" s="5"/>
       <c r="U424" s="5"/>
@@ -31470,7 +31689,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R425" s="5"/>
+      <c r="R425" s="43"/>
       <c r="S425" s="5"/>
       <c r="T425" s="5"/>
       <c r="U425" s="5"/>
@@ -31536,7 +31755,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R426" s="5"/>
+      <c r="R426" s="43"/>
       <c r="S426" s="5"/>
       <c r="T426" s="5"/>
       <c r="U426" s="5"/>
@@ -31602,7 +31821,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R427" s="5"/>
+      <c r="R427" s="43"/>
       <c r="S427" s="5"/>
       <c r="T427" s="5"/>
       <c r="U427" s="5"/>
@@ -31668,7 +31887,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R428" s="5"/>
+      <c r="R428" s="43"/>
       <c r="S428" s="5"/>
       <c r="T428" s="5"/>
       <c r="U428" s="5"/>
@@ -31734,7 +31953,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R429" s="5"/>
+      <c r="R429" s="43"/>
       <c r="S429" s="5"/>
       <c r="T429" s="5"/>
       <c r="U429" s="5"/>
@@ -31800,7 +32019,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R430" s="5"/>
+      <c r="R430" s="43"/>
       <c r="S430" s="5"/>
       <c r="T430" s="5"/>
       <c r="U430" s="5"/>
@@ -31866,7 +32085,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R431" s="5"/>
+      <c r="R431" s="43"/>
       <c r="S431" s="5"/>
       <c r="T431" s="5"/>
       <c r="U431" s="5"/>
@@ -31932,7 +32151,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R432" s="5"/>
+      <c r="R432" s="43"/>
       <c r="S432" s="5"/>
       <c r="T432" s="5"/>
       <c r="U432" s="5"/>
@@ -31998,7 +32217,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R433" s="5"/>
+      <c r="R433" s="43"/>
       <c r="S433" s="5"/>
       <c r="T433" s="5"/>
       <c r="U433" s="5"/>
@@ -32064,7 +32283,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R434" s="5"/>
+      <c r="R434" s="43"/>
       <c r="S434" s="5"/>
       <c r="T434" s="5"/>
       <c r="U434" s="5"/>
@@ -32130,7 +32349,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R435" s="5"/>
+      <c r="R435" s="43"/>
       <c r="S435" s="5"/>
       <c r="T435" s="5"/>
       <c r="U435" s="5"/>
@@ -32196,7 +32415,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R436" s="5"/>
+      <c r="R436" s="43"/>
       <c r="S436" s="5"/>
       <c r="T436" s="5"/>
       <c r="U436" s="5"/>
@@ -32262,7 +32481,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R437" s="5"/>
+      <c r="R437" s="43"/>
       <c r="S437" s="5"/>
       <c r="T437" s="5"/>
       <c r="U437" s="5"/>
@@ -32328,7 +32547,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R438" s="5"/>
+      <c r="R438" s="43"/>
       <c r="S438" s="5"/>
       <c r="T438" s="5"/>
       <c r="U438" s="5"/>
@@ -32394,7 +32613,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R439" s="5"/>
+      <c r="R439" s="43"/>
       <c r="S439" s="5"/>
       <c r="T439" s="5"/>
       <c r="U439" s="5"/>
@@ -32460,7 +32679,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R440" s="5"/>
+      <c r="R440" s="43"/>
       <c r="S440" s="5"/>
       <c r="T440" s="5"/>
       <c r="U440" s="5"/>
@@ -32526,7 +32745,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R441" s="5"/>
+      <c r="R441" s="43"/>
       <c r="S441" s="5"/>
       <c r="T441" s="5"/>
       <c r="U441" s="5"/>
@@ -32592,7 +32811,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R442" s="5"/>
+      <c r="R442" s="43"/>
       <c r="S442" s="5"/>
       <c r="T442" s="5"/>
       <c r="U442" s="5"/>
@@ -32658,7 +32877,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R443" s="5"/>
+      <c r="R443" s="43"/>
       <c r="S443" s="5"/>
       <c r="T443" s="5"/>
       <c r="U443" s="5"/>
@@ -32724,7 +32943,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R444" s="5"/>
+      <c r="R444" s="43"/>
       <c r="S444" s="5"/>
       <c r="T444" s="5"/>
       <c r="U444" s="5"/>
@@ -32790,7 +33009,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R445" s="5"/>
+      <c r="R445" s="43"/>
       <c r="S445" s="5"/>
       <c r="T445" s="5"/>
       <c r="U445" s="5"/>
@@ -32856,7 +33075,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R446" s="5"/>
+      <c r="R446" s="43"/>
       <c r="S446" s="5"/>
       <c r="T446" s="5"/>
       <c r="U446" s="5"/>
@@ -32922,7 +33141,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R447" s="5"/>
+      <c r="R447" s="43"/>
       <c r="S447" s="5"/>
       <c r="T447" s="5"/>
       <c r="U447" s="5"/>
@@ -32988,7 +33207,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R448" s="5"/>
+      <c r="R448" s="43"/>
       <c r="S448" s="5"/>
       <c r="T448" s="5"/>
       <c r="U448" s="5"/>
@@ -33054,7 +33273,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R449" s="5"/>
+      <c r="R449" s="43"/>
       <c r="S449" s="5"/>
       <c r="T449" s="5"/>
       <c r="U449" s="5"/>
@@ -33120,7 +33339,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R450" s="5"/>
+      <c r="R450" s="43"/>
       <c r="S450" s="5"/>
       <c r="T450" s="5"/>
       <c r="U450" s="5"/>
@@ -33186,7 +33405,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R451" s="5"/>
+      <c r="R451" s="43"/>
       <c r="S451" s="5"/>
       <c r="T451" s="5"/>
       <c r="U451" s="5"/>
@@ -33252,7 +33471,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R452" s="5"/>
+      <c r="R452" s="43"/>
       <c r="S452" s="5"/>
       <c r="T452" s="5"/>
       <c r="U452" s="5"/>
@@ -33318,7 +33537,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R453" s="5"/>
+      <c r="R453" s="43"/>
       <c r="S453" s="5"/>
       <c r="T453" s="5"/>
       <c r="U453" s="5"/>
@@ -33384,7 +33603,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R454" s="5"/>
+      <c r="R454" s="43"/>
       <c r="S454" s="5"/>
       <c r="T454" s="5"/>
       <c r="U454" s="5"/>
@@ -33450,7 +33669,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R455" s="5"/>
+      <c r="R455" s="43"/>
       <c r="S455" s="5"/>
       <c r="T455" s="5"/>
       <c r="U455" s="5"/>
@@ -33516,7 +33735,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R456" s="5"/>
+      <c r="R456" s="43"/>
       <c r="S456" s="5"/>
       <c r="T456" s="5"/>
       <c r="U456" s="5"/>
@@ -33582,7 +33801,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R457" s="5"/>
+      <c r="R457" s="43"/>
       <c r="S457" s="5"/>
       <c r="T457" s="5"/>
       <c r="U457" s="5"/>
@@ -33648,7 +33867,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R458" s="5"/>
+      <c r="R458" s="43"/>
       <c r="S458" s="5"/>
       <c r="T458" s="5"/>
       <c r="U458" s="5"/>
@@ -33714,7 +33933,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R459" s="5"/>
+      <c r="R459" s="43"/>
       <c r="S459" s="5"/>
       <c r="T459" s="5"/>
       <c r="U459" s="5"/>
@@ -33780,7 +33999,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R460" s="5"/>
+      <c r="R460" s="43"/>
       <c r="S460" s="5"/>
       <c r="T460" s="5"/>
       <c r="U460" s="5"/>
@@ -33846,7 +34065,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R461" s="5"/>
+      <c r="R461" s="43"/>
       <c r="S461" s="5"/>
       <c r="T461" s="5"/>
       <c r="U461" s="5"/>
@@ -33912,7 +34131,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R462" s="5"/>
+      <c r="R462" s="43"/>
       <c r="S462" s="5"/>
       <c r="T462" s="5"/>
       <c r="U462" s="5"/>
@@ -33978,7 +34197,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R463" s="5"/>
+      <c r="R463" s="43"/>
       <c r="S463" s="5"/>
       <c r="T463" s="5"/>
       <c r="U463" s="5"/>
@@ -34044,7 +34263,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R464" s="5"/>
+      <c r="R464" s="43"/>
       <c r="S464" s="5"/>
       <c r="T464" s="5"/>
       <c r="U464" s="5"/>
@@ -34110,7 +34329,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R465" s="5"/>
+      <c r="R465" s="43"/>
       <c r="S465" s="5"/>
       <c r="T465" s="5"/>
       <c r="U465" s="5"/>
@@ -34176,7 +34395,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R466" s="5"/>
+      <c r="R466" s="43"/>
       <c r="S466" s="5"/>
       <c r="T466" s="5"/>
       <c r="U466" s="5"/>
@@ -34242,7 +34461,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R467" s="5"/>
+      <c r="R467" s="43"/>
       <c r="S467" s="5"/>
       <c r="T467" s="5"/>
       <c r="U467" s="5"/>
@@ -34308,7 +34527,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R468" s="5"/>
+      <c r="R468" s="43"/>
       <c r="S468" s="5"/>
       <c r="T468" s="5"/>
       <c r="U468" s="5"/>
@@ -34374,7 +34593,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R469" s="5"/>
+      <c r="R469" s="43"/>
       <c r="S469" s="5"/>
       <c r="T469" s="5"/>
       <c r="U469" s="5"/>
@@ -34440,7 +34659,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R470" s="5"/>
+      <c r="R470" s="43"/>
       <c r="S470" s="5"/>
       <c r="T470" s="5"/>
       <c r="U470" s="5"/>
@@ -34506,7 +34725,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R471" s="5"/>
+      <c r="R471" s="43"/>
       <c r="S471" s="5"/>
       <c r="T471" s="5"/>
       <c r="U471" s="5"/>
@@ -34572,7 +34791,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R472" s="5"/>
+      <c r="R472" s="43"/>
       <c r="S472" s="5"/>
       <c r="T472" s="5"/>
       <c r="U472" s="5"/>
@@ -34638,7 +34857,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R473" s="5"/>
+      <c r="R473" s="43"/>
       <c r="S473" s="5"/>
       <c r="T473" s="5"/>
       <c r="U473" s="5"/>
@@ -34704,7 +34923,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R474" s="5"/>
+      <c r="R474" s="43"/>
       <c r="S474" s="5"/>
       <c r="T474" s="5"/>
       <c r="U474" s="5"/>
@@ -34770,7 +34989,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R475" s="5"/>
+      <c r="R475" s="43"/>
       <c r="S475" s="5"/>
       <c r="T475" s="5"/>
       <c r="U475" s="5"/>
@@ -34836,7 +35055,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R476" s="5"/>
+      <c r="R476" s="43"/>
       <c r="S476" s="5"/>
       <c r="T476" s="5"/>
       <c r="U476" s="5"/>
@@ -34902,7 +35121,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R477" s="5"/>
+      <c r="R477" s="43"/>
       <c r="S477" s="5"/>
       <c r="T477" s="5"/>
       <c r="U477" s="5"/>
@@ -34968,7 +35187,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R478" s="5"/>
+      <c r="R478" s="43"/>
       <c r="S478" s="5"/>
       <c r="T478" s="5"/>
       <c r="U478" s="5"/>
@@ -35034,7 +35253,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R479" s="5"/>
+      <c r="R479" s="43"/>
       <c r="S479" s="5"/>
       <c r="T479" s="5"/>
       <c r="U479" s="5"/>
@@ -35100,7 +35319,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R480" s="5"/>
+      <c r="R480" s="43"/>
       <c r="S480" s="5"/>
       <c r="T480" s="5"/>
       <c r="U480" s="5"/>
@@ -35166,7 +35385,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R481" s="5"/>
+      <c r="R481" s="43"/>
       <c r="S481" s="5"/>
       <c r="T481" s="5"/>
       <c r="U481" s="5"/>
@@ -35232,7 +35451,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R482" s="5"/>
+      <c r="R482" s="43"/>
       <c r="S482" s="5"/>
       <c r="T482" s="5"/>
       <c r="U482" s="5"/>
@@ -35298,7 +35517,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R483" s="5"/>
+      <c r="R483" s="43"/>
       <c r="S483" s="5"/>
       <c r="T483" s="5"/>
       <c r="U483" s="5"/>
@@ -35364,7 +35583,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R484" s="5"/>
+      <c r="R484" s="43"/>
       <c r="S484" s="5"/>
       <c r="T484" s="5"/>
       <c r="U484" s="5"/>
@@ -35430,7 +35649,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R485" s="5"/>
+      <c r="R485" s="43"/>
       <c r="S485" s="5"/>
       <c r="T485" s="5"/>
       <c r="U485" s="5"/>
@@ -35496,7 +35715,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R486" s="5"/>
+      <c r="R486" s="43"/>
       <c r="S486" s="5"/>
       <c r="T486" s="5"/>
       <c r="U486" s="5"/>
@@ -35562,7 +35781,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R487" s="5"/>
+      <c r="R487" s="43"/>
       <c r="S487" s="5"/>
       <c r="T487" s="5"/>
       <c r="U487" s="5"/>
@@ -35628,7 +35847,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R488" s="5"/>
+      <c r="R488" s="43"/>
       <c r="S488" s="5"/>
       <c r="T488" s="5"/>
       <c r="U488" s="5"/>
@@ -35694,7 +35913,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R489" s="5"/>
+      <c r="R489" s="43"/>
       <c r="S489" s="5"/>
       <c r="T489" s="5"/>
       <c r="U489" s="5"/>
@@ -35760,7 +35979,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R490" s="5"/>
+      <c r="R490" s="43"/>
       <c r="S490" s="5"/>
       <c r="T490" s="5"/>
       <c r="U490" s="5"/>
@@ -35826,7 +36045,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R491" s="5"/>
+      <c r="R491" s="43"/>
       <c r="S491" s="5"/>
       <c r="T491" s="5"/>
       <c r="U491" s="5"/>
@@ -35892,7 +36111,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R492" s="5"/>
+      <c r="R492" s="43"/>
       <c r="S492" s="5"/>
       <c r="T492" s="5"/>
       <c r="U492" s="5"/>
@@ -35958,7 +36177,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R493" s="5"/>
+      <c r="R493" s="43"/>
       <c r="S493" s="5"/>
       <c r="T493" s="5"/>
       <c r="U493" s="5"/>
@@ -36024,7 +36243,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R494" s="5"/>
+      <c r="R494" s="43"/>
       <c r="S494" s="5"/>
       <c r="T494" s="5"/>
       <c r="U494" s="5"/>
@@ -36090,7 +36309,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R495" s="5"/>
+      <c r="R495" s="43"/>
       <c r="S495" s="5"/>
       <c r="T495" s="5"/>
       <c r="U495" s="5"/>
@@ -36156,7 +36375,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R496" s="5"/>
+      <c r="R496" s="43"/>
       <c r="S496" s="5"/>
       <c r="T496" s="5"/>
       <c r="U496" s="5"/>
@@ -36222,7 +36441,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R497" s="5"/>
+      <c r="R497" s="43"/>
       <c r="S497" s="5"/>
       <c r="T497" s="5"/>
       <c r="U497" s="5"/>
@@ -36288,7 +36507,7 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>no</v>
       </c>
-      <c r="R498" s="5"/>
+      <c r="R498" s="43"/>
       <c r="S498" s="5"/>
       <c r="T498" s="5"/>
       <c r="U498" s="5"/>
@@ -36354,10 +36573,15 @@
         <f>IF(AND(Dmart_Sales_Data[[#This Row],[customer_type2]]="Member",OR(Dmart_Sales_Data[[#This Row],[payment_mode]]="UPI",Dmart_Sales_Data[[#This Row],[payment_mode]]="Card")),"yes","no")</f>
         <v>yes</v>
       </c>
-      <c r="R499" s="5"/>
+      <c r="R499" s="43"/>
       <c r="S499" s="5"/>
-      <c r="T499" s="5"/>
-      <c r="U499" s="5"/>
+      <c r="T499" s="50" t="s">
+        <v>680</v>
+      </c>
+      <c r="U499" s="54">
+        <f>SUM(Saless)</f>
+        <v>1322669.1900000023</v>
+      </c>
       <c r="V499" s="5"/>
       <c r="W499" s="5"/>
       <c r="X499" s="5"/>
@@ -36366,7 +36590,7 @@
       <c r="AA499" s="5"/>
       <c r="AB499" s="5"/>
     </row>
-    <row r="500" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="5"/>
       <c r="B500" s="23"/>
       <c r="C500" s="5"/>
@@ -36386,8 +36610,13 @@
       <c r="Q500" s="5"/>
       <c r="R500" s="5"/>
       <c r="S500" s="5"/>
-      <c r="T500" s="5"/>
-      <c r="U500" s="5"/>
+      <c r="T500" s="50" t="s">
+        <v>681</v>
+      </c>
+      <c r="U500" s="54" cm="1">
+        <f t="array" ref="U500">SUBTOTAL(9,Saless)</f>
+        <v>1322669.1900000023</v>
+      </c>
       <c r="V500" s="5"/>
       <c r="W500" s="5"/>
     </row>
@@ -48892,7 +49121,7 @@
       <c r="W1000" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="E1:E1048576 F1:F499">
     <cfRule type="top10" dxfId="4" priority="2" bottom="1" rank="10"/>
     <cfRule type="top10" dxfId="3" priority="3" rank="10"/>
@@ -49128,7 +49357,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -49199,7 +49428,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -49270,16 +49499,68 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41824523-D9F3-4140-9DD2-41B5D565F751}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B2" s="31" t="s">
+        <v>679</v>
+      </c>
+      <c r="H2" s="58"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="29">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="29">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="29">
+        <v>23</v>
+      </c>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="29">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="29">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f>SUBTOTAL(101,B3:B8)</f>
+        <v>96.333333333333329</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f>SUBTOTAL(9,B3:B8)</f>
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:B8" xr:uid="{41824523-D9F3-4140-9DD2-41B5D565F751}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -49290,10 +49571,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.109375" customWidth="1"/>
-    <col min="2" max="3" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.44140625" customWidth="1"/>
     <col min="7" max="7" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -49447,43 +49729,86 @@
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
     </row>
-    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
+    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="45"/>
     </row>
-    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-    </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-    </row>
-    <row r="17" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
+    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>578</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>677</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B14" s="28" t="s">
+        <v>579</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>584</v>
+      </c>
+      <c r="D14" s="56">
+        <v>1001</v>
+      </c>
+      <c r="F14" s="29">
+        <f>COUNTIF(C14:C18,"Ankit")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B15" s="28" t="s">
+        <v>580</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>585</v>
+      </c>
+      <c r="D15" s="56">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B16" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>586</v>
+      </c>
+      <c r="D16" s="56">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="B17" s="28" t="s">
+        <v>582</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>587</v>
+      </c>
+      <c r="D17" s="56">
+        <v>1002</v>
+      </c>
     </row>
     <row r="18" spans="2:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
+      <c r="B18" s="56" t="s">
+        <v>580</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>585</v>
+      </c>
+      <c r="D18" s="56">
+        <v>1002</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -50071,7 +50396,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E9">
     <sortCondition ref="D2:D9" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="E2:E9">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>50000</formula>
@@ -50082,4 +50407,210 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD98AE6-A688-4F29-87FC-1CF77EBCF783}">
+  <dimension ref="A2:H16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>605</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>579</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>629</v>
+      </c>
+      <c r="E2" s="61" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="29">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>610</v>
+      </c>
+      <c r="C3" s="32">
+        <v>70000</v>
+      </c>
+      <c r="D3" s="59">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="36">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="29">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>611</v>
+      </c>
+      <c r="C4" s="32">
+        <v>50000</v>
+      </c>
+      <c r="D4" s="59">
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="36">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="29">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>612</v>
+      </c>
+      <c r="C5" s="32">
+        <v>45000</v>
+      </c>
+      <c r="D5" s="59">
+        <v>0</v>
+      </c>
+      <c r="E5" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="29">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>613</v>
+      </c>
+      <c r="C6" s="32">
+        <v>75000</v>
+      </c>
+      <c r="D6" s="59">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="36">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="29">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>628</v>
+      </c>
+      <c r="C7" s="32">
+        <v>55000</v>
+      </c>
+      <c r="D7" s="59">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="29">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <f>MATCH(C2,A2:E2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <f>C15</f>
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="C10" s="63" t="s">
+        <v>682</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>579</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="29">
+        <v>1005</v>
+      </c>
+      <c r="D11" s="29">
+        <f>VLOOKUP(C11,A2:E7,MATCH(C2,A2:E2,0), FALSE)</f>
+        <v>55000</v>
+      </c>
+      <c r="E11" s="29">
+        <f>VLOOKUP(C11,A3:E7,MATCH(E2,A2:E2,0),FALSE)</f>
+        <v>2750</v>
+      </c>
+      <c r="H11">
+        <f>MATCH(C2,A2:E2,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B12" s="63" t="s">
+        <v>684</v>
+      </c>
+      <c r="C12">
+        <f>MATCH(B6,B3:B7,0)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B13" s="64" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="B14" s="63" t="s">
+        <v>682</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>579</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>633</v>
+      </c>
+      <c r="E14" s="29"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="29">
+        <v>1001</v>
+      </c>
+      <c r="C15" s="29">
+        <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),MATCH(C2,A2:E2,0))</f>
+        <v>70000</v>
+      </c>
+      <c r="D15" s="29">
+        <f>INDEX(A3:E7,MATCH(B15,A3:A7,0),MATCH(E2,A2:E2,0))</f>
+        <v>7000</v>
+      </c>
+      <c r="E15" s="29"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="F16" s="62"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11 B15" xr:uid="{F2EDDFF2-4254-4F09-B918-63D39C07AF33}">
+      <formula1>$A$3:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B963C782-4AB3-4EA3-AECE-26F7A2C28218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5236414-9483-489F-B9CE-E9B28524A456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4765" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4766" uniqueCount="704">
   <si>
     <t>Column1</t>
   </si>
@@ -6502,7 +6502,9 @@
       <c r="U41" s="73" t="s">
         <v>579</v>
       </c>
-      <c r="V41" s="5"/>
+      <c r="V41" s="73" t="s">
+        <v>687</v>
+      </c>
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
       <c r="Y41" s="5"/>
@@ -6568,13 +6570,16 @@
       <c r="R42" s="43"/>
       <c r="S42" s="43"/>
       <c r="T42" s="42" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="U42" s="5">
-        <f>VLOOKUP(T42,A1:Q499,MATCH(U41,1:1,0),FALSE)</f>
-        <v>713.49</v>
-      </c>
-      <c r="V42" s="5"/>
+        <f>VLOOKUP($T$42,Dmart_Sales_Data[#All],MATCH(U41,Dmart_Sales_Data[[#Headers],[Column1]:[discount_given]],0),FALSE)</f>
+        <v>2566.1799999999998</v>
+      </c>
+      <c r="V42" s="5">
+        <f>VLOOKUP($T$42,Dmart_Sales_Data[#All],MATCH(V41,Dmart_Sales_Data[[#Headers],[Column1]:[discount_given]],0),FALSE)</f>
+        <v>578.94000000000005</v>
+      </c>
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
       <c r="Y42" s="5"/>
@@ -50261,6 +50266,11 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T42" xr:uid="{136F02E8-2E99-4EE5-B737-5CA315AB15CD}">
+      <formula1>$A$2:$A$499</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
